--- a/assets/demand_template.xlsx
+++ b/assets/demand_template.xlsx
@@ -8,19 +8,22 @@
   </bookViews>
   <sheets>
     <sheet name="需求单" sheetId="1" r:id="rId1"/>
+    <sheet name="SAP导出昆明可用件库存" sheetId="2" r:id="rId2"/>
+    <sheet name="工程师操作介绍" sheetId="3" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">需求单!$A$1:$I$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">SAP导出昆明可用件库存!$A$1:$BI$6046</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="46">
   <si>
     <t>机务二队定检需求单（XXXX.XX.XX）
 （B-XXXX XXA）</t>
@@ -156,24 +159,55 @@
   <si>
     <t>调配数量</t>
   </si>
+  <si>
+    <t>进入库存查询会比较慢，最长达10min。因此需求单航材数量较少的建议采用原来的手动搜索方式</t>
+  </si>
+  <si>
+    <t>双击填充若失败，可用拖动填充</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="44">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -451,12 +485,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0C0C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -654,6 +694,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -1012,21 +1067,6 @@
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1361,172 +1401,199 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="20" fillId="0" borderId="0">
+    <xf numFmtId="42" fontId="24" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="50">
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="50">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="20" fillId="0" borderId="0">
+    <xf numFmtId="44" fontId="24" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0">
+    <xf numFmtId="41" fontId="24" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0">
+    <xf numFmtId="43" fontId="24" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="51">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="24" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="52">
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="51">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="52">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="53">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="11" borderId="54">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="11" borderId="50">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="52">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="12" borderId="55">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="52">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="53">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="56">
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="57">
+    <xf numFmtId="0" fontId="37" fillId="12" borderId="54">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="38" fillId="12" borderId="50">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="39" fillId="13" borderId="55">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="56">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="57">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="42" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="43" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1534,228 +1601,228 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1767,39 +1834,39 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1861,6 +1928,197 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>29845</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>20955</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5839460" cy="6062345"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10431145" y="201930"/>
+          <a:ext cx="5839460" cy="6062345"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>461010</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="10848975" cy="3062605"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="461010" y="6578600"/>
+          <a:ext cx="10848975" cy="3062605"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>415290</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>52705</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="9515475" cy="9686925"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="415290" y="9888855"/>
+          <a:ext cx="9515475" cy="9686925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>34925</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>147320</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="15655925" cy="8476615"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="图片 4"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="34925" y="19756120"/>
+          <a:ext cx="15655925" cy="8476615"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3727450" cy="2372995"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="图片 5"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9525" y="9525"/>
+          <a:ext cx="3727450" cy="2372995"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>404495</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>635</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5743575" cy="6296025"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="图片 6"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4119245" y="635"/>
+          <a:ext cx="5743575" cy="6296025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2140,669 +2398,669 @@
   <dimension ref="A1:I81"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="15" style="1" customWidth="1"/>
-    <col min="2" max="2" width="34.6615384615385" style="1" customWidth="1"/>
-    <col min="3" max="3" width="26.3307692307692" style="1" customWidth="1"/>
-    <col min="4" max="4" width="38.6692307692308" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.8307692307692" style="1" customWidth="1"/>
-    <col min="6" max="7" width="26.1615384615385" style="1" customWidth="1"/>
-    <col min="8" max="9" width="24.3307692307692" style="2" customWidth="1"/>
-    <col min="11" max="40" width="8.43076923076923" style="3" customWidth="1"/>
+    <col min="1" max="1" width="15" style="10" customWidth="1"/>
+    <col min="2" max="2" width="34.6615384615385" style="10" customWidth="1"/>
+    <col min="3" max="3" width="26.3307692307692" style="10" customWidth="1"/>
+    <col min="4" max="4" width="38.6692307692308" style="10" customWidth="1"/>
+    <col min="5" max="5" width="13.8307692307692" style="10" customWidth="1"/>
+    <col min="6" max="7" width="26.1615384615385" style="10" customWidth="1"/>
+    <col min="8" max="9" width="24.3307692307692" style="11" customWidth="1"/>
+    <col min="11" max="40" width="8.43076923076923" style="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="67" customHeight="1" spans="1:9">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="75"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="84"/>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:9">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="76"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="85"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:9">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="10" t="s">
+      <c r="B3" s="18"/>
+      <c r="C3" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="11"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="10" t="s">
+      <c r="E3" s="20"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="77"/>
+      <c r="I3" s="86"/>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:9">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="14" t="s">
+      <c r="B4" s="22"/>
+      <c r="C4" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="15"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="14" t="s">
+      <c r="D4" s="24"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="17"/>
-      <c r="I4" s="78"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="87"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:9">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="20" t="s">
+      <c r="B5" s="28"/>
+      <c r="C5" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="22"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="20" t="s">
+      <c r="E5" s="31"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="23"/>
-      <c r="I5" s="79"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="88"/>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:9">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="20" t="s">
+      <c r="B6" s="28"/>
+      <c r="C6" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="21"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="20" t="s">
+      <c r="D6" s="30"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="23"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="88"/>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="20" t="s">
+      <c r="B7" s="28"/>
+      <c r="C7" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="21"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="20" t="s">
+      <c r="D7" s="30"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="23"/>
-      <c r="I7" s="79"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="88"/>
     </row>
     <row r="8" ht="25" customHeight="1" spans="1:9">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="20" t="s">
+      <c r="B8" s="28"/>
+      <c r="C8" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="21"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="20" t="s">
+      <c r="D8" s="30"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="23"/>
-      <c r="I8" s="79"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="88"/>
     </row>
     <row r="9" ht="25" customHeight="1" spans="1:9">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="20" t="s">
+      <c r="B9" s="28"/>
+      <c r="C9" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="21"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="20" t="s">
+      <c r="D9" s="30"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="H9" s="23"/>
-      <c r="I9" s="79"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="88"/>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:9">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="20" t="s">
+      <c r="B10" s="28"/>
+      <c r="C10" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="21"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="20" t="s">
+      <c r="D10" s="30"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="H10" s="23"/>
-      <c r="I10" s="79"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="88"/>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:9">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="20" t="s">
+      <c r="B11" s="28"/>
+      <c r="C11" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="21"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="20" t="s">
+      <c r="D11" s="30"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="H11" s="23"/>
-      <c r="I11" s="79"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="88"/>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:9">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="25"/>
-      <c r="C12" s="26" t="s">
+      <c r="B12" s="34"/>
+      <c r="C12" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="27"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="26" t="s">
+      <c r="D12" s="36"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="29"/>
-      <c r="I12" s="80"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="89"/>
     </row>
     <row r="13" ht="33" customHeight="1" spans="1:9">
-      <c r="A13" s="30" t="s">
+      <c r="A13" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="31"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="31"/>
-      <c r="I13" s="81"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="90"/>
     </row>
     <row r="14" ht="40" customHeight="1" spans="1:9">
-      <c r="A14" s="32" t="s">
+      <c r="A14" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="33" t="s">
+      <c r="D14" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="33" t="s">
+      <c r="E14" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="F14" s="33" t="s">
+      <c r="F14" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="34" t="s">
+      <c r="G14" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="H14" s="33" t="s">
+      <c r="H14" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="I14" s="82" t="s">
+      <c r="I14" s="91" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1" spans="1:9">
-      <c r="A15" s="35" t="s">
+      <c r="A15" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="36"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="83"/>
+      <c r="B15" s="45"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="46"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="92"/>
     </row>
     <row r="16" ht="34" customHeight="1" spans="1:9">
-      <c r="A16" s="40"/>
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="84"/>
+      <c r="A16" s="49"/>
+      <c r="B16" s="50"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="55"/>
+      <c r="I16" s="93"/>
     </row>
     <row r="17" ht="34" customHeight="1" spans="1:9">
-      <c r="A17" s="40"/>
-      <c r="B17" s="41"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="46"/>
-      <c r="I17" s="84"/>
+      <c r="A17" s="49"/>
+      <c r="B17" s="50"/>
+      <c r="C17" s="50"/>
+      <c r="D17" s="50"/>
+      <c r="E17" s="50"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="55"/>
+      <c r="I17" s="93"/>
     </row>
     <row r="18" ht="34" customHeight="1" spans="1:9">
-      <c r="A18" s="47" t="s">
+      <c r="A18" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="41"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="48"/>
-      <c r="I18" s="84"/>
+      <c r="B18" s="50"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="53"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="57"/>
+      <c r="I18" s="93"/>
     </row>
     <row r="19" ht="34" customHeight="1" spans="1:9">
-      <c r="A19" s="40"/>
-      <c r="B19" s="41"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="84"/>
+      <c r="A19" s="49"/>
+      <c r="B19" s="50"/>
+      <c r="C19" s="50"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="55"/>
+      <c r="I19" s="93"/>
     </row>
     <row r="20" ht="34" customHeight="1" spans="1:9">
-      <c r="A20" s="40"/>
-      <c r="B20" s="41"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="84"/>
+      <c r="A20" s="49"/>
+      <c r="B20" s="50"/>
+      <c r="C20" s="50"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="55"/>
+      <c r="I20" s="93"/>
     </row>
     <row r="21" ht="34" customHeight="1" spans="1:9">
-      <c r="A21" s="49" t="s">
+      <c r="A21" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="41"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="50"/>
-      <c r="I21" s="84"/>
+      <c r="B21" s="50"/>
+      <c r="C21" s="50"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="50"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="59"/>
+      <c r="I21" s="93"/>
     </row>
     <row r="22" ht="34" customHeight="1" spans="1:9">
-      <c r="A22" s="40"/>
-      <c r="B22" s="41"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="84"/>
+      <c r="A22" s="49"/>
+      <c r="B22" s="50"/>
+      <c r="C22" s="50"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="52"/>
+      <c r="F22" s="53"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="55"/>
+      <c r="I22" s="93"/>
     </row>
     <row r="23" ht="34" customHeight="1" spans="1:9">
-      <c r="A23" s="40"/>
-      <c r="B23" s="41"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="84"/>
+      <c r="A23" s="49"/>
+      <c r="B23" s="50"/>
+      <c r="C23" s="50"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="55"/>
+      <c r="I23" s="93"/>
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:9">
-      <c r="A24" s="51" t="s">
+      <c r="A24" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="52" t="s">
+      <c r="B24" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="75"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="84"/>
     </row>
     <row r="25" ht="47" customHeight="1" spans="1:9">
-      <c r="A25" s="53" t="s">
+      <c r="A25" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="B25" s="34" t="s">
+      <c r="B25" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="C25" s="34" t="s">
+      <c r="C25" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="33" t="s">
+      <c r="D25" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="E25" s="33" t="s">
+      <c r="E25" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="F25" s="33" t="s">
+      <c r="F25" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="G25" s="34" t="s">
+      <c r="G25" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="H25" s="54" t="s">
+      <c r="H25" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="I25" s="85" t="s">
+      <c r="I25" s="94" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="26" ht="31" customHeight="1" spans="1:9">
-      <c r="A26" s="55" t="s">
+      <c r="A26" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="56"/>
-      <c r="C26" s="56"/>
-      <c r="D26" s="56"/>
-      <c r="E26" s="56"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="59"/>
-      <c r="I26" s="86" t="str">
+      <c r="B26" s="65"/>
+      <c r="C26" s="65"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="65"/>
+      <c r="F26" s="66"/>
+      <c r="G26" s="67"/>
+      <c r="H26" s="68"/>
+      <c r="I26" s="95" t="str">
         <f>IF($C26="","",SUMIFS([1]SAP导出昆明可用件库存!$R:$R,[1]SAP导出昆明可用件库存!$B:$B,C26,[1]SAP导出昆明可用件库存!$G:$G,"昆明可用库"))</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="31" customHeight="1" spans="1:9">
-      <c r="A27" s="60"/>
-      <c r="B27" s="61"/>
-      <c r="C27" s="61"/>
-      <c r="D27" s="61"/>
-      <c r="E27" s="61"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="63"/>
-      <c r="H27" s="64"/>
-      <c r="I27" s="86" t="str">
+      <c r="A27" s="69"/>
+      <c r="B27" s="70"/>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="72"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="95" t="str">
         <f>IF($C27="","",SUMIFS([1]SAP导出昆明可用件库存!$R:$R,[1]SAP导出昆明可用件库存!$B:$B,C27,[1]SAP导出昆明可用件库存!$G:$G,"昆明可用库"))</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="31" customHeight="1" spans="1:9">
-      <c r="A28" s="60"/>
-      <c r="B28" s="61"/>
-      <c r="C28" s="61"/>
-      <c r="D28" s="61"/>
-      <c r="E28" s="61"/>
-      <c r="F28" s="65"/>
-      <c r="G28" s="63"/>
-      <c r="H28" s="64"/>
-      <c r="I28" s="86" t="str">
+      <c r="A28" s="69"/>
+      <c r="B28" s="70"/>
+      <c r="C28" s="70"/>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="74"/>
+      <c r="G28" s="72"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="95" t="str">
         <f>IF($C28="","",SUMIFS([1]SAP导出昆明可用件库存!$R:$R,[1]SAP导出昆明可用件库存!$B:$B,C28,[1]SAP导出昆明可用件库存!$G:$G,"昆明可用库"))</f>
         <v/>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" ht="26" customHeight="1" spans="1:9">
-      <c r="A29" s="66" t="s">
+    <row r="29" s="10" customFormat="1" ht="26" customHeight="1" spans="1:9">
+      <c r="A29" s="75" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="61"/>
-      <c r="C29" s="61"/>
-      <c r="D29" s="61"/>
-      <c r="E29" s="61"/>
-      <c r="F29" s="62"/>
-      <c r="G29" s="63"/>
-      <c r="H29" s="67"/>
-      <c r="I29" s="86" t="str">
+      <c r="B29" s="70"/>
+      <c r="C29" s="70"/>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="72"/>
+      <c r="H29" s="76"/>
+      <c r="I29" s="95" t="str">
         <f>IF($C29="","",SUMIFS([1]SAP导出昆明可用件库存!$R:$R,[1]SAP导出昆明可用件库存!$B:$B,C29,[1]SAP导出昆明可用件库存!$G:$G,"昆明可用库"))</f>
         <v/>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" ht="26" customHeight="1" spans="1:9">
-      <c r="A30" s="60"/>
-      <c r="B30" s="61"/>
-      <c r="C30" s="61"/>
-      <c r="D30" s="61"/>
-      <c r="E30" s="61"/>
-      <c r="F30" s="62"/>
-      <c r="G30" s="63"/>
-      <c r="H30" s="64"/>
-      <c r="I30" s="86" t="str">
+    <row r="30" s="10" customFormat="1" ht="26" customHeight="1" spans="1:9">
+      <c r="A30" s="69"/>
+      <c r="B30" s="70"/>
+      <c r="C30" s="70"/>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="72"/>
+      <c r="H30" s="73"/>
+      <c r="I30" s="95" t="str">
         <f>IF($C30="","",SUMIFS([1]SAP导出昆明可用件库存!$R:$R,[1]SAP导出昆明可用件库存!$B:$B,C30,[1]SAP导出昆明可用件库存!$G:$G,"昆明可用库"))</f>
         <v/>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" ht="26" customHeight="1" spans="1:9">
-      <c r="A31" s="60"/>
-      <c r="B31" s="61"/>
-      <c r="C31" s="61"/>
-      <c r="D31" s="61"/>
-      <c r="E31" s="61"/>
-      <c r="F31" s="65"/>
-      <c r="G31" s="63"/>
-      <c r="H31" s="64"/>
-      <c r="I31" s="86" t="str">
+    <row r="31" s="10" customFormat="1" ht="26" customHeight="1" spans="1:9">
+      <c r="A31" s="69"/>
+      <c r="B31" s="70"/>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="74"/>
+      <c r="G31" s="72"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="95" t="str">
         <f>IF($C31="","",SUMIFS([1]SAP导出昆明可用件库存!$R:$R,[1]SAP导出昆明可用件库存!$B:$B,C31,[1]SAP导出昆明可用件库存!$G:$G,"昆明可用库"))</f>
         <v/>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" ht="34" customHeight="1" spans="1:9">
-      <c r="A32" s="68" t="s">
+    <row r="32" s="10" customFormat="1" ht="34" customHeight="1" spans="1:9">
+      <c r="A32" s="77" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="61"/>
-      <c r="C32" s="61"/>
-      <c r="D32" s="61"/>
-      <c r="E32" s="61"/>
-      <c r="F32" s="62"/>
-      <c r="G32" s="63"/>
-      <c r="H32" s="67"/>
-      <c r="I32" s="86" t="str">
+      <c r="B32" s="70"/>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="72"/>
+      <c r="H32" s="76"/>
+      <c r="I32" s="95" t="str">
         <f>IF($C32="","",SUMIFS([1]SAP导出昆明可用件库存!$R:$R,[1]SAP导出昆明可用件库存!$B:$B,C32,[1]SAP导出昆明可用件库存!$G:$G,"昆明可用库"))</f>
         <v/>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" ht="34" customHeight="1" spans="1:9">
-      <c r="A33" s="60"/>
-      <c r="B33" s="61"/>
-      <c r="C33" s="61"/>
-      <c r="D33" s="61"/>
-      <c r="E33" s="61"/>
-      <c r="F33" s="62"/>
-      <c r="G33" s="63"/>
-      <c r="H33" s="64"/>
-      <c r="I33" s="86" t="str">
+    <row r="33" s="10" customFormat="1" ht="34" customHeight="1" spans="1:9">
+      <c r="A33" s="69"/>
+      <c r="B33" s="70"/>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="72"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="95" t="str">
         <f>IF($C33="","",SUMIFS([1]SAP导出昆明可用件库存!$R:$R,[1]SAP导出昆明可用件库存!$B:$B,C33,[1]SAP导出昆明可用件库存!$G:$G,"昆明可用库"))</f>
         <v/>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" ht="34" customHeight="1" spans="1:9">
-      <c r="A34" s="60"/>
-      <c r="B34" s="61"/>
-      <c r="C34" s="61"/>
-      <c r="D34" s="61"/>
-      <c r="E34" s="61"/>
-      <c r="F34" s="65"/>
-      <c r="G34" s="63"/>
-      <c r="H34" s="64"/>
-      <c r="I34" s="86" t="str">
+    <row r="34" s="10" customFormat="1" ht="34" customHeight="1" spans="1:9">
+      <c r="A34" s="69"/>
+      <c r="B34" s="70"/>
+      <c r="C34" s="70"/>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="74"/>
+      <c r="G34" s="72"/>
+      <c r="H34" s="73"/>
+      <c r="I34" s="95" t="str">
         <f>IF($C34="","",SUMIFS([1]SAP导出昆明可用件库存!$R:$R,[1]SAP导出昆明可用件库存!$B:$B,C34,[1]SAP导出昆明可用件库存!$G:$G,"昆明可用库"))</f>
         <v/>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" ht="26" customHeight="1" spans="1:9">
-      <c r="A35" s="69" t="s">
+    <row r="35" s="10" customFormat="1" ht="26" customHeight="1" spans="1:9">
+      <c r="A35" s="78" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="31"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="81"/>
+      <c r="B35" s="40"/>
+      <c r="C35" s="40"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="40"/>
+      <c r="H35" s="40"/>
+      <c r="I35" s="90"/>
     </row>
     <row r="36" ht="47" customHeight="1" spans="1:9">
-      <c r="A36" s="53" t="s">
+      <c r="A36" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="34" t="s">
+      <c r="B36" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="C36" s="34" t="s">
+      <c r="C36" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="D36" s="33" t="s">
+      <c r="D36" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="E36" s="33" t="s">
+      <c r="E36" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="F36" s="33" t="s">
+      <c r="F36" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="G36" s="34" t="s">
+      <c r="G36" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="H36" s="54" t="s">
+      <c r="H36" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="I36" s="85" t="s">
+      <c r="I36" s="94" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="37" ht="25" customHeight="1" spans="1:9">
-      <c r="A37" s="70" t="s">
+      <c r="A37" s="79" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="71"/>
-      <c r="C37" s="71"/>
-      <c r="D37" s="71"/>
-      <c r="E37" s="71"/>
-      <c r="F37" s="72"/>
-      <c r="G37" s="72"/>
-      <c r="H37" s="72"/>
-      <c r="I37" s="87" t="str">
+      <c r="B37" s="80"/>
+      <c r="C37" s="80"/>
+      <c r="D37" s="80"/>
+      <c r="E37" s="80"/>
+      <c r="F37" s="81"/>
+      <c r="G37" s="81"/>
+      <c r="H37" s="81"/>
+      <c r="I37" s="96" t="str">
         <f>IF($C37="","",SUMIFS([1]SAP导出昆明可用件库存!$R:$R,[1]SAP导出昆明可用件库存!$B:$B,C37,[1]SAP导出昆明可用件库存!$G:$G,"昆明可用库"))</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1" spans="1:9">
-      <c r="A38" s="73"/>
-      <c r="B38" s="71"/>
-      <c r="C38" s="71"/>
-      <c r="D38" s="71"/>
-      <c r="E38" s="71"/>
-      <c r="F38" s="72"/>
-      <c r="G38" s="72"/>
-      <c r="H38" s="72"/>
-      <c r="I38" s="87" t="str">
+      <c r="A38" s="82"/>
+      <c r="B38" s="80"/>
+      <c r="C38" s="80"/>
+      <c r="D38" s="80"/>
+      <c r="E38" s="80"/>
+      <c r="F38" s="81"/>
+      <c r="G38" s="81"/>
+      <c r="H38" s="81"/>
+      <c r="I38" s="96" t="str">
         <f>IF($C38="","",SUMIFS([1]SAP导出昆明可用件库存!$R:$R,[1]SAP导出昆明可用件库存!$B:$B,C38,[1]SAP导出昆明可用件库存!$G:$G,"昆明可用库"))</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1" spans="1:9">
-      <c r="A39" s="70" t="s">
+      <c r="A39" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="71"/>
-      <c r="C39" s="71"/>
-      <c r="D39" s="71"/>
-      <c r="E39" s="71"/>
-      <c r="F39" s="72"/>
-      <c r="G39" s="72"/>
-      <c r="H39" s="72"/>
-      <c r="I39" s="87" t="str">
+      <c r="B39" s="80"/>
+      <c r="C39" s="80"/>
+      <c r="D39" s="80"/>
+      <c r="E39" s="80"/>
+      <c r="F39" s="81"/>
+      <c r="G39" s="81"/>
+      <c r="H39" s="81"/>
+      <c r="I39" s="96" t="str">
         <f>IF($C39="","",SUMIFS([1]SAP导出昆明可用件库存!$R:$R,[1]SAP导出昆明可用件库存!$B:$B,C39,[1]SAP导出昆明可用件库存!$G:$G,"昆明可用库"))</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1" spans="1:9">
-      <c r="A40" s="73"/>
-      <c r="B40" s="71"/>
-      <c r="C40" s="74"/>
-      <c r="D40" s="72"/>
-      <c r="E40" s="72"/>
-      <c r="F40" s="72"/>
-      <c r="G40" s="72"/>
-      <c r="H40" s="72"/>
-      <c r="I40" s="87" t="str">
+      <c r="A40" s="82"/>
+      <c r="B40" s="80"/>
+      <c r="C40" s="83"/>
+      <c r="D40" s="81"/>
+      <c r="E40" s="81"/>
+      <c r="F40" s="81"/>
+      <c r="G40" s="81"/>
+      <c r="H40" s="81"/>
+      <c r="I40" s="96" t="str">
         <f>IF($C40="","",SUMIFS([1]SAP导出昆明可用件库存!$R:$R,[1]SAP导出昆明可用件库存!$B:$B,C40,[1]SAP导出昆明可用件库存!$G:$G,"昆明可用库"))</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1" spans="1:9">
-      <c r="A41" s="70" t="s">
+      <c r="A41" s="79" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="71"/>
-      <c r="C41" s="74"/>
-      <c r="D41" s="72"/>
-      <c r="E41" s="72"/>
-      <c r="F41" s="72"/>
-      <c r="G41" s="72"/>
-      <c r="H41" s="72"/>
-      <c r="I41" s="87" t="str">
+      <c r="B41" s="80"/>
+      <c r="C41" s="83"/>
+      <c r="D41" s="81"/>
+      <c r="E41" s="81"/>
+      <c r="F41" s="81"/>
+      <c r="G41" s="81"/>
+      <c r="H41" s="81"/>
+      <c r="I41" s="96" t="str">
         <f>IF($C41="","",SUMIFS([1]SAP导出昆明可用件库存!$R:$R,[1]SAP导出昆明可用件库存!$B:$B,C41,[1]SAP导出昆明可用件库存!$G:$G,"昆明可用库"))</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="25" customHeight="1" spans="1:9">
-      <c r="A42" s="73"/>
-      <c r="B42" s="71"/>
-      <c r="C42" s="74"/>
-      <c r="D42" s="72"/>
-      <c r="E42" s="72"/>
-      <c r="F42" s="72"/>
-      <c r="G42" s="72"/>
-      <c r="H42" s="72"/>
-      <c r="I42" s="87" t="str">
+      <c r="A42" s="82"/>
+      <c r="B42" s="80"/>
+      <c r="C42" s="83"/>
+      <c r="D42" s="81"/>
+      <c r="E42" s="81"/>
+      <c r="F42" s="81"/>
+      <c r="G42" s="81"/>
+      <c r="H42" s="81"/>
+      <c r="I42" s="96" t="str">
         <f>IF($C42="","",SUMIFS([1]SAP导出昆明可用件库存!$R:$R,[1]SAP导出昆明可用件库存!$B:$B,C42,[1]SAP导出昆明可用件库存!$G:$G,"昆明可用库"))</f>
         <v/>
       </c>
@@ -2865,4 +3123,3108 @@
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:AN200"/>
+  <sheetFormatPr defaultColWidth="7.83076923076923" defaultRowHeight="12.75" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="5.16923076923077" style="5" customWidth="1"/>
+    <col min="2" max="2" width="26.1692307692308" style="5" customWidth="1"/>
+    <col min="3" max="3" width="17.5" style="5" customWidth="1"/>
+    <col min="4" max="4" width="5.16923076923077" style="5" customWidth="1"/>
+    <col min="5" max="5" width="36.6692307692308" style="5" customWidth="1"/>
+    <col min="6" max="6" width="4.33076923076923" style="5" customWidth="1"/>
+    <col min="7" max="7" width="10.6692307692308" style="5" customWidth="1"/>
+    <col min="8" max="10" width="10.5" style="5" customWidth="1"/>
+    <col min="11" max="13" width="11.3307692307692" style="5" customWidth="1"/>
+    <col min="14" max="14" width="4.33076923076923" style="5" customWidth="1"/>
+    <col min="15" max="15" width="5.16923076923077" style="5" customWidth="1"/>
+    <col min="16" max="16" width="10.5" style="5" customWidth="1"/>
+    <col min="17" max="17" width="5.16923076923077" style="5" customWidth="1"/>
+    <col min="18" max="18" width="8.66923076923077" style="5" customWidth="1"/>
+    <col min="19" max="19" width="7" style="5" customWidth="1"/>
+    <col min="20" max="21" width="7.83076923076923" style="5" customWidth="1"/>
+    <col min="22" max="25" width="6.16923076923077" style="5" customWidth="1"/>
+    <col min="26" max="27" width="8.66923076923077" style="5" customWidth="1"/>
+    <col min="28" max="28" width="6.16923076923077" style="5" customWidth="1"/>
+    <col min="29" max="31" width="5.16923076923077" style="5" customWidth="1"/>
+    <col min="32" max="32" width="7" style="5" customWidth="1"/>
+    <col min="33" max="33" width="9.66923076923077" style="5" customWidth="1"/>
+    <col min="34" max="34" width="6.16923076923077" style="5" customWidth="1"/>
+    <col min="35" max="35" width="13.1692307692308" style="5" customWidth="1"/>
+    <col min="36" max="37" width="5.16923076923077" style="5" customWidth="1"/>
+    <col min="38" max="38" width="14.8307692307692" style="5" customWidth="1"/>
+    <col min="39" max="39" width="17.5" style="5" customWidth="1"/>
+    <col min="40" max="40" width="3.5" style="5" customWidth="1"/>
+    <col min="41" max="16384" width="7.83076923076923" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customHeight="1" spans="1:40">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="6"/>
+      <c r="X1" s="6"/>
+      <c r="Y1" s="6"/>
+      <c r="Z1" s="6"/>
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6"/>
+      <c r="AD1" s="6"/>
+      <c r="AE1" s="6"/>
+      <c r="AF1" s="6"/>
+      <c r="AG1" s="6"/>
+      <c r="AH1" s="6"/>
+      <c r="AI1" s="6"/>
+      <c r="AJ1" s="6"/>
+      <c r="AK1" s="6"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+    </row>
+    <row r="2" customHeight="1" spans="1:27">
+      <c r="A2" s="7"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="R2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+    </row>
+    <row r="3" customHeight="1" spans="1:27">
+      <c r="A3" s="7"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="R3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="9"/>
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="9"/>
+    </row>
+    <row r="4" customHeight="1" spans="1:27">
+      <c r="A4" s="7"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="R4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="9"/>
+      <c r="Z4" s="9"/>
+      <c r="AA4" s="9"/>
+    </row>
+    <row r="5" customHeight="1" spans="1:27">
+      <c r="A5" s="7"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="R5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="9"/>
+      <c r="Z5" s="9"/>
+      <c r="AA5" s="9"/>
+    </row>
+    <row r="6" customHeight="1" spans="1:27">
+      <c r="A6" s="7"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="R6" s="9"/>
+      <c r="T6" s="9"/>
+      <c r="U6" s="9"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="9"/>
+      <c r="X6" s="9"/>
+      <c r="Y6" s="9"/>
+      <c r="Z6" s="9"/>
+      <c r="AA6" s="9"/>
+    </row>
+    <row r="7" customHeight="1" spans="1:27">
+      <c r="A7" s="7"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="R7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="9"/>
+      <c r="Z7" s="9"/>
+      <c r="AA7" s="9"/>
+    </row>
+    <row r="8" customHeight="1" spans="1:27">
+      <c r="A8" s="7"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="R8" s="9"/>
+      <c r="T8" s="9"/>
+      <c r="U8" s="9"/>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="9"/>
+      <c r="Y8" s="9"/>
+      <c r="Z8" s="9"/>
+      <c r="AA8" s="9"/>
+    </row>
+    <row r="9" customHeight="1" spans="1:27">
+      <c r="A9" s="7"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="R9" s="9"/>
+      <c r="T9" s="9"/>
+      <c r="U9" s="9"/>
+      <c r="V9" s="9"/>
+      <c r="W9" s="9"/>
+      <c r="X9" s="9"/>
+      <c r="Y9" s="9"/>
+      <c r="Z9" s="9"/>
+      <c r="AA9" s="9"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:27">
+      <c r="A10" s="7"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="R10" s="9"/>
+      <c r="T10" s="9"/>
+      <c r="U10" s="9"/>
+      <c r="V10" s="9"/>
+      <c r="W10" s="9"/>
+      <c r="X10" s="9"/>
+      <c r="Y10" s="9"/>
+      <c r="Z10" s="9"/>
+      <c r="AA10" s="9"/>
+    </row>
+    <row r="11" customHeight="1" spans="1:27">
+      <c r="A11" s="7"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="R11" s="9"/>
+      <c r="T11" s="9"/>
+      <c r="U11" s="9"/>
+      <c r="V11" s="9"/>
+      <c r="W11" s="9"/>
+      <c r="X11" s="9"/>
+      <c r="Y11" s="9"/>
+      <c r="Z11" s="9"/>
+      <c r="AA11" s="9"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:27">
+      <c r="A12" s="7"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="R12" s="9"/>
+      <c r="T12" s="9"/>
+      <c r="U12" s="9"/>
+      <c r="V12" s="9"/>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+    </row>
+    <row r="13" customHeight="1" spans="1:27">
+      <c r="A13" s="7"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="R13" s="9"/>
+      <c r="T13" s="9"/>
+      <c r="U13" s="9"/>
+      <c r="V13" s="9"/>
+      <c r="W13" s="9"/>
+      <c r="X13" s="9"/>
+      <c r="Y13" s="9"/>
+      <c r="Z13" s="9"/>
+      <c r="AA13" s="9"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:27">
+      <c r="A14" s="7"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="R14" s="9"/>
+      <c r="T14" s="9"/>
+      <c r="U14" s="9"/>
+      <c r="V14" s="9"/>
+      <c r="W14" s="9"/>
+      <c r="X14" s="9"/>
+      <c r="Y14" s="9"/>
+      <c r="Z14" s="9"/>
+      <c r="AA14" s="9"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:27">
+      <c r="A15" s="7"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="R15" s="9"/>
+      <c r="T15" s="9"/>
+      <c r="U15" s="9"/>
+      <c r="V15" s="9"/>
+      <c r="W15" s="9"/>
+      <c r="X15" s="9"/>
+      <c r="Y15" s="9"/>
+      <c r="Z15" s="9"/>
+      <c r="AA15" s="9"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:27">
+      <c r="A16" s="7"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="R16" s="9"/>
+      <c r="T16" s="9"/>
+      <c r="U16" s="9"/>
+      <c r="V16" s="9"/>
+      <c r="W16" s="9"/>
+      <c r="X16" s="9"/>
+      <c r="Y16" s="9"/>
+      <c r="Z16" s="9"/>
+      <c r="AA16" s="9"/>
+    </row>
+    <row r="17" customHeight="1" spans="1:27">
+      <c r="A17" s="7"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="R17" s="9"/>
+      <c r="T17" s="9"/>
+      <c r="U17" s="9"/>
+      <c r="V17" s="9"/>
+      <c r="W17" s="9"/>
+      <c r="X17" s="9"/>
+      <c r="Y17" s="9"/>
+      <c r="Z17" s="9"/>
+      <c r="AA17" s="9"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:27">
+      <c r="A18" s="7"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="R18" s="9"/>
+      <c r="T18" s="9"/>
+      <c r="U18" s="9"/>
+      <c r="V18" s="9"/>
+      <c r="W18" s="9"/>
+      <c r="X18" s="9"/>
+      <c r="Y18" s="9"/>
+      <c r="Z18" s="9"/>
+      <c r="AA18" s="9"/>
+    </row>
+    <row r="19" customHeight="1" spans="1:27">
+      <c r="A19" s="7"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="R19" s="9"/>
+      <c r="T19" s="9"/>
+      <c r="U19" s="9"/>
+      <c r="V19" s="9"/>
+      <c r="W19" s="9"/>
+      <c r="X19" s="9"/>
+      <c r="Y19" s="9"/>
+      <c r="Z19" s="9"/>
+      <c r="AA19" s="9"/>
+    </row>
+    <row r="20" customHeight="1" spans="1:27">
+      <c r="A20" s="7"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="R20" s="9"/>
+      <c r="T20" s="9"/>
+      <c r="U20" s="9"/>
+      <c r="V20" s="9"/>
+      <c r="W20" s="9"/>
+      <c r="X20" s="9"/>
+      <c r="Y20" s="9"/>
+      <c r="Z20" s="9"/>
+      <c r="AA20" s="9"/>
+    </row>
+    <row r="21" customHeight="1" spans="1:27">
+      <c r="A21" s="7"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="R21" s="9"/>
+      <c r="T21" s="9"/>
+      <c r="U21" s="9"/>
+      <c r="V21" s="9"/>
+      <c r="W21" s="9"/>
+      <c r="X21" s="9"/>
+      <c r="Y21" s="9"/>
+      <c r="Z21" s="9"/>
+      <c r="AA21" s="9"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:27">
+      <c r="A22" s="7"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="R22" s="9"/>
+      <c r="T22" s="9"/>
+      <c r="U22" s="9"/>
+      <c r="V22" s="9"/>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:27">
+      <c r="A23" s="7"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="R23" s="9"/>
+      <c r="T23" s="9"/>
+      <c r="U23" s="9"/>
+      <c r="V23" s="9"/>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:27">
+      <c r="A24" s="7"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="R24" s="9"/>
+      <c r="T24" s="9"/>
+      <c r="U24" s="9"/>
+      <c r="V24" s="9"/>
+      <c r="W24" s="9"/>
+      <c r="X24" s="9"/>
+      <c r="Y24" s="9"/>
+      <c r="Z24" s="9"/>
+      <c r="AA24" s="9"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:27">
+      <c r="A25" s="7"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="R25" s="9"/>
+      <c r="T25" s="9"/>
+      <c r="U25" s="9"/>
+      <c r="V25" s="9"/>
+      <c r="W25" s="9"/>
+      <c r="X25" s="9"/>
+      <c r="Y25" s="9"/>
+      <c r="Z25" s="9"/>
+      <c r="AA25" s="9"/>
+    </row>
+    <row r="26" customHeight="1" spans="1:27">
+      <c r="A26" s="7"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="R26" s="9"/>
+      <c r="T26" s="9"/>
+      <c r="U26" s="9"/>
+      <c r="V26" s="9"/>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+    </row>
+    <row r="27" customHeight="1" spans="1:27">
+      <c r="A27" s="7"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="R27" s="9"/>
+      <c r="T27" s="9"/>
+      <c r="U27" s="9"/>
+      <c r="V27" s="9"/>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+    </row>
+    <row r="28" customHeight="1" spans="1:27">
+      <c r="A28" s="7"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="R28" s="9"/>
+      <c r="T28" s="9"/>
+      <c r="U28" s="9"/>
+      <c r="V28" s="9"/>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+    </row>
+    <row r="29" customHeight="1" spans="1:27">
+      <c r="A29" s="7"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="R29" s="9"/>
+      <c r="T29" s="9"/>
+      <c r="U29" s="9"/>
+      <c r="V29" s="9"/>
+      <c r="W29" s="9"/>
+      <c r="X29" s="9"/>
+      <c r="Y29" s="9"/>
+      <c r="Z29" s="9"/>
+      <c r="AA29" s="9"/>
+    </row>
+    <row r="30" customHeight="1" spans="1:27">
+      <c r="A30" s="7"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="R30" s="9"/>
+      <c r="T30" s="9"/>
+      <c r="U30" s="9"/>
+      <c r="V30" s="9"/>
+      <c r="W30" s="9"/>
+      <c r="X30" s="9"/>
+      <c r="Y30" s="9"/>
+      <c r="Z30" s="9"/>
+      <c r="AA30" s="9"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:27">
+      <c r="A31" s="7"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="8"/>
+      <c r="R31" s="9"/>
+      <c r="T31" s="9"/>
+      <c r="U31" s="9"/>
+      <c r="V31" s="9"/>
+      <c r="W31" s="9"/>
+      <c r="X31" s="9"/>
+      <c r="Y31" s="9"/>
+      <c r="Z31" s="9"/>
+      <c r="AA31" s="9"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:27">
+      <c r="A32" s="7"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="R32" s="9"/>
+      <c r="T32" s="9"/>
+      <c r="U32" s="9"/>
+      <c r="V32" s="9"/>
+      <c r="W32" s="9"/>
+      <c r="X32" s="9"/>
+      <c r="Y32" s="9"/>
+      <c r="Z32" s="9"/>
+      <c r="AA32" s="9"/>
+    </row>
+    <row r="33" customHeight="1" spans="1:27">
+      <c r="A33" s="7"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
+      <c r="R33" s="9"/>
+      <c r="T33" s="9"/>
+      <c r="U33" s="9"/>
+      <c r="V33" s="9"/>
+      <c r="W33" s="9"/>
+      <c r="X33" s="9"/>
+      <c r="Y33" s="9"/>
+      <c r="Z33" s="9"/>
+      <c r="AA33" s="9"/>
+    </row>
+    <row r="34" customHeight="1" spans="1:27">
+      <c r="A34" s="7"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="R34" s="9"/>
+      <c r="T34" s="9"/>
+      <c r="U34" s="9"/>
+      <c r="V34" s="9"/>
+      <c r="W34" s="9"/>
+      <c r="X34" s="9"/>
+      <c r="Y34" s="9"/>
+      <c r="Z34" s="9"/>
+      <c r="AA34" s="9"/>
+    </row>
+    <row r="35" customHeight="1" spans="1:27">
+      <c r="A35" s="7"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
+      <c r="R35" s="9"/>
+      <c r="T35" s="9"/>
+      <c r="U35" s="9"/>
+      <c r="V35" s="9"/>
+      <c r="W35" s="9"/>
+      <c r="X35" s="9"/>
+      <c r="Y35" s="9"/>
+      <c r="Z35" s="9"/>
+      <c r="AA35" s="9"/>
+    </row>
+    <row r="36" customHeight="1" spans="1:27">
+      <c r="A36" s="7"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="8"/>
+      <c r="R36" s="9"/>
+      <c r="T36" s="9"/>
+      <c r="U36" s="9"/>
+      <c r="V36" s="9"/>
+      <c r="W36" s="9"/>
+      <c r="X36" s="9"/>
+      <c r="Y36" s="9"/>
+      <c r="Z36" s="9"/>
+      <c r="AA36" s="9"/>
+    </row>
+    <row r="37" customHeight="1" spans="1:27">
+      <c r="A37" s="7"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="8"/>
+      <c r="M37" s="8"/>
+      <c r="R37" s="9"/>
+      <c r="T37" s="9"/>
+      <c r="U37" s="9"/>
+      <c r="V37" s="9"/>
+      <c r="W37" s="9"/>
+      <c r="X37" s="9"/>
+      <c r="Y37" s="9"/>
+      <c r="Z37" s="9"/>
+      <c r="AA37" s="9"/>
+    </row>
+    <row r="38" customHeight="1" spans="1:27">
+      <c r="A38" s="7"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="8"/>
+      <c r="M38" s="8"/>
+      <c r="R38" s="9"/>
+      <c r="T38" s="9"/>
+      <c r="U38" s="9"/>
+      <c r="V38" s="9"/>
+      <c r="W38" s="9"/>
+      <c r="X38" s="9"/>
+      <c r="Y38" s="9"/>
+      <c r="Z38" s="9"/>
+      <c r="AA38" s="9"/>
+    </row>
+    <row r="39" customHeight="1" spans="1:27">
+      <c r="A39" s="7"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="8"/>
+      <c r="M39" s="8"/>
+      <c r="R39" s="9"/>
+      <c r="T39" s="9"/>
+      <c r="U39" s="9"/>
+      <c r="V39" s="9"/>
+      <c r="W39" s="9"/>
+      <c r="X39" s="9"/>
+      <c r="Y39" s="9"/>
+      <c r="Z39" s="9"/>
+      <c r="AA39" s="9"/>
+    </row>
+    <row r="40" customHeight="1" spans="1:27">
+      <c r="A40" s="7"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="8"/>
+      <c r="M40" s="8"/>
+      <c r="R40" s="9"/>
+      <c r="T40" s="9"/>
+      <c r="U40" s="9"/>
+      <c r="V40" s="9"/>
+      <c r="W40" s="9"/>
+      <c r="X40" s="9"/>
+      <c r="Y40" s="9"/>
+      <c r="Z40" s="9"/>
+      <c r="AA40" s="9"/>
+    </row>
+    <row r="41" customHeight="1" spans="1:27">
+      <c r="A41" s="7"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="8"/>
+      <c r="M41" s="8"/>
+      <c r="R41" s="9"/>
+      <c r="T41" s="9"/>
+      <c r="U41" s="9"/>
+      <c r="V41" s="9"/>
+      <c r="W41" s="9"/>
+      <c r="X41" s="9"/>
+      <c r="Y41" s="9"/>
+      <c r="Z41" s="9"/>
+      <c r="AA41" s="9"/>
+    </row>
+    <row r="42" customHeight="1" spans="1:27">
+      <c r="A42" s="7"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="8"/>
+      <c r="M42" s="8"/>
+      <c r="R42" s="9"/>
+      <c r="T42" s="9"/>
+      <c r="U42" s="9"/>
+      <c r="V42" s="9"/>
+      <c r="W42" s="9"/>
+      <c r="X42" s="9"/>
+      <c r="Y42" s="9"/>
+      <c r="Z42" s="9"/>
+      <c r="AA42" s="9"/>
+    </row>
+    <row r="43" customHeight="1" spans="1:27">
+      <c r="A43" s="7"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="8"/>
+      <c r="R43" s="9"/>
+      <c r="T43" s="9"/>
+      <c r="U43" s="9"/>
+      <c r="V43" s="9"/>
+      <c r="W43" s="9"/>
+      <c r="X43" s="9"/>
+      <c r="Y43" s="9"/>
+      <c r="Z43" s="9"/>
+      <c r="AA43" s="9"/>
+    </row>
+    <row r="44" customHeight="1" spans="1:27">
+      <c r="A44" s="7"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="8"/>
+      <c r="M44" s="8"/>
+      <c r="R44" s="9"/>
+      <c r="T44" s="9"/>
+      <c r="U44" s="9"/>
+      <c r="V44" s="9"/>
+      <c r="W44" s="9"/>
+      <c r="X44" s="9"/>
+      <c r="Y44" s="9"/>
+      <c r="Z44" s="9"/>
+      <c r="AA44" s="9"/>
+    </row>
+    <row r="45" customHeight="1" spans="1:27">
+      <c r="A45" s="7"/>
+      <c r="K45" s="8"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="8"/>
+      <c r="R45" s="9"/>
+      <c r="T45" s="9"/>
+      <c r="U45" s="9"/>
+      <c r="V45" s="9"/>
+      <c r="W45" s="9"/>
+      <c r="X45" s="9"/>
+      <c r="Y45" s="9"/>
+      <c r="Z45" s="9"/>
+      <c r="AA45" s="9"/>
+    </row>
+    <row r="46" customHeight="1" spans="1:27">
+      <c r="A46" s="7"/>
+      <c r="K46" s="8"/>
+      <c r="L46" s="8"/>
+      <c r="M46" s="8"/>
+      <c r="R46" s="9"/>
+      <c r="T46" s="9"/>
+      <c r="U46" s="9"/>
+      <c r="V46" s="9"/>
+      <c r="W46" s="9"/>
+      <c r="X46" s="9"/>
+      <c r="Y46" s="9"/>
+      <c r="Z46" s="9"/>
+      <c r="AA46" s="9"/>
+    </row>
+    <row r="47" customHeight="1" spans="1:27">
+      <c r="A47" s="7"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="8"/>
+      <c r="M47" s="8"/>
+      <c r="R47" s="9"/>
+      <c r="T47" s="9"/>
+      <c r="U47" s="9"/>
+      <c r="V47" s="9"/>
+      <c r="W47" s="9"/>
+      <c r="X47" s="9"/>
+      <c r="Y47" s="9"/>
+      <c r="Z47" s="9"/>
+      <c r="AA47" s="9"/>
+    </row>
+    <row r="48" customHeight="1" spans="1:27">
+      <c r="A48" s="7"/>
+      <c r="K48" s="8"/>
+      <c r="L48" s="8"/>
+      <c r="M48" s="8"/>
+      <c r="R48" s="9"/>
+      <c r="T48" s="9"/>
+      <c r="U48" s="9"/>
+      <c r="V48" s="9"/>
+      <c r="W48" s="9"/>
+      <c r="X48" s="9"/>
+      <c r="Y48" s="9"/>
+      <c r="Z48" s="9"/>
+      <c r="AA48" s="9"/>
+    </row>
+    <row r="49" customHeight="1" spans="1:27">
+      <c r="A49" s="7"/>
+      <c r="K49" s="8"/>
+      <c r="L49" s="8"/>
+      <c r="M49" s="8"/>
+      <c r="R49" s="9"/>
+      <c r="T49" s="9"/>
+      <c r="U49" s="9"/>
+      <c r="V49" s="9"/>
+      <c r="W49" s="9"/>
+      <c r="X49" s="9"/>
+      <c r="Y49" s="9"/>
+      <c r="Z49" s="9"/>
+      <c r="AA49" s="9"/>
+    </row>
+    <row r="50" customHeight="1" spans="1:27">
+      <c r="A50" s="7"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="8"/>
+      <c r="M50" s="8"/>
+      <c r="R50" s="9"/>
+      <c r="T50" s="9"/>
+      <c r="U50" s="9"/>
+      <c r="V50" s="9"/>
+      <c r="W50" s="9"/>
+      <c r="X50" s="9"/>
+      <c r="Y50" s="9"/>
+      <c r="Z50" s="9"/>
+      <c r="AA50" s="9"/>
+    </row>
+    <row r="51" customHeight="1" spans="1:27">
+      <c r="A51" s="7"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="R51" s="9"/>
+      <c r="T51" s="9"/>
+      <c r="U51" s="9"/>
+      <c r="V51" s="9"/>
+      <c r="W51" s="9"/>
+      <c r="X51" s="9"/>
+      <c r="Y51" s="9"/>
+      <c r="Z51" s="9"/>
+      <c r="AA51" s="9"/>
+    </row>
+    <row r="52" customHeight="1" spans="1:27">
+      <c r="A52" s="7"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+      <c r="R52" s="9"/>
+      <c r="T52" s="9"/>
+      <c r="U52" s="9"/>
+      <c r="V52" s="9"/>
+      <c r="W52" s="9"/>
+      <c r="X52" s="9"/>
+      <c r="Y52" s="9"/>
+      <c r="Z52" s="9"/>
+      <c r="AA52" s="9"/>
+    </row>
+    <row r="53" customHeight="1" spans="1:27">
+      <c r="A53" s="7"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+      <c r="M53" s="8"/>
+      <c r="R53" s="9"/>
+      <c r="T53" s="9"/>
+      <c r="U53" s="9"/>
+      <c r="V53" s="9"/>
+      <c r="W53" s="9"/>
+      <c r="X53" s="9"/>
+      <c r="Y53" s="9"/>
+      <c r="Z53" s="9"/>
+      <c r="AA53" s="9"/>
+    </row>
+    <row r="54" customHeight="1" spans="1:27">
+      <c r="A54" s="7"/>
+      <c r="K54" s="8"/>
+      <c r="L54" s="8"/>
+      <c r="M54" s="8"/>
+      <c r="R54" s="9"/>
+      <c r="T54" s="9"/>
+      <c r="U54" s="9"/>
+      <c r="V54" s="9"/>
+      <c r="W54" s="9"/>
+      <c r="X54" s="9"/>
+      <c r="Y54" s="9"/>
+      <c r="Z54" s="9"/>
+      <c r="AA54" s="9"/>
+    </row>
+    <row r="55" customHeight="1" spans="1:27">
+      <c r="A55" s="7"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="8"/>
+      <c r="M55" s="8"/>
+      <c r="R55" s="9"/>
+      <c r="T55" s="9"/>
+      <c r="U55" s="9"/>
+      <c r="V55" s="9"/>
+      <c r="W55" s="9"/>
+      <c r="X55" s="9"/>
+      <c r="Y55" s="9"/>
+      <c r="Z55" s="9"/>
+      <c r="AA55" s="9"/>
+    </row>
+    <row r="56" customHeight="1" spans="1:27">
+      <c r="A56" s="7"/>
+      <c r="K56" s="8"/>
+      <c r="L56" s="8"/>
+      <c r="M56" s="8"/>
+      <c r="R56" s="9"/>
+      <c r="T56" s="9"/>
+      <c r="U56" s="9"/>
+      <c r="V56" s="9"/>
+      <c r="W56" s="9"/>
+      <c r="X56" s="9"/>
+      <c r="Y56" s="9"/>
+      <c r="Z56" s="9"/>
+      <c r="AA56" s="9"/>
+    </row>
+    <row r="57" customHeight="1" spans="1:27">
+      <c r="A57" s="7"/>
+      <c r="K57" s="8"/>
+      <c r="L57" s="8"/>
+      <c r="M57" s="8"/>
+      <c r="R57" s="9"/>
+      <c r="T57" s="9"/>
+      <c r="U57" s="9"/>
+      <c r="V57" s="9"/>
+      <c r="W57" s="9"/>
+      <c r="X57" s="9"/>
+      <c r="Y57" s="9"/>
+      <c r="Z57" s="9"/>
+      <c r="AA57" s="9"/>
+    </row>
+    <row r="58" customHeight="1" spans="1:27">
+      <c r="A58" s="7"/>
+      <c r="K58" s="8"/>
+      <c r="L58" s="8"/>
+      <c r="M58" s="8"/>
+      <c r="R58" s="9"/>
+      <c r="T58" s="9"/>
+      <c r="U58" s="9"/>
+      <c r="V58" s="9"/>
+      <c r="W58" s="9"/>
+      <c r="X58" s="9"/>
+      <c r="Y58" s="9"/>
+      <c r="Z58" s="9"/>
+      <c r="AA58" s="9"/>
+    </row>
+    <row r="59" customHeight="1" spans="1:27">
+      <c r="A59" s="7"/>
+      <c r="K59" s="8"/>
+      <c r="L59" s="8"/>
+      <c r="M59" s="8"/>
+      <c r="R59" s="9"/>
+      <c r="T59" s="9"/>
+      <c r="U59" s="9"/>
+      <c r="V59" s="9"/>
+      <c r="W59" s="9"/>
+      <c r="X59" s="9"/>
+      <c r="Y59" s="9"/>
+      <c r="Z59" s="9"/>
+      <c r="AA59" s="9"/>
+    </row>
+    <row r="60" customHeight="1" spans="1:27">
+      <c r="A60" s="7"/>
+      <c r="K60" s="8"/>
+      <c r="L60" s="8"/>
+      <c r="M60" s="8"/>
+      <c r="R60" s="9"/>
+      <c r="T60" s="9"/>
+      <c r="U60" s="9"/>
+      <c r="V60" s="9"/>
+      <c r="W60" s="9"/>
+      <c r="X60" s="9"/>
+      <c r="Y60" s="9"/>
+      <c r="Z60" s="9"/>
+      <c r="AA60" s="9"/>
+    </row>
+    <row r="61" customHeight="1" spans="1:27">
+      <c r="A61" s="7"/>
+      <c r="K61" s="8"/>
+      <c r="L61" s="8"/>
+      <c r="M61" s="8"/>
+      <c r="R61" s="9"/>
+      <c r="T61" s="9"/>
+      <c r="U61" s="9"/>
+      <c r="V61" s="9"/>
+      <c r="W61" s="9"/>
+      <c r="X61" s="9"/>
+      <c r="Y61" s="9"/>
+      <c r="Z61" s="9"/>
+      <c r="AA61" s="9"/>
+    </row>
+    <row r="62" customHeight="1" spans="1:27">
+      <c r="A62" s="7"/>
+      <c r="K62" s="8"/>
+      <c r="L62" s="8"/>
+      <c r="M62" s="8"/>
+      <c r="R62" s="9"/>
+      <c r="T62" s="9"/>
+      <c r="U62" s="9"/>
+      <c r="V62" s="9"/>
+      <c r="W62" s="9"/>
+      <c r="X62" s="9"/>
+      <c r="Y62" s="9"/>
+      <c r="Z62" s="9"/>
+      <c r="AA62" s="9"/>
+    </row>
+    <row r="63" customHeight="1" spans="1:27">
+      <c r="A63" s="7"/>
+      <c r="K63" s="8"/>
+      <c r="L63" s="8"/>
+      <c r="M63" s="8"/>
+      <c r="R63" s="9"/>
+      <c r="T63" s="9"/>
+      <c r="U63" s="9"/>
+      <c r="V63" s="9"/>
+      <c r="W63" s="9"/>
+      <c r="X63" s="9"/>
+      <c r="Y63" s="9"/>
+      <c r="Z63" s="9"/>
+      <c r="AA63" s="9"/>
+    </row>
+    <row r="64" customHeight="1" spans="1:27">
+      <c r="A64" s="7"/>
+      <c r="K64" s="8"/>
+      <c r="L64" s="8"/>
+      <c r="M64" s="8"/>
+      <c r="R64" s="9"/>
+      <c r="T64" s="9"/>
+      <c r="U64" s="9"/>
+      <c r="V64" s="9"/>
+      <c r="W64" s="9"/>
+      <c r="X64" s="9"/>
+      <c r="Y64" s="9"/>
+      <c r="Z64" s="9"/>
+      <c r="AA64" s="9"/>
+    </row>
+    <row r="65" customHeight="1" spans="1:27">
+      <c r="A65" s="7"/>
+      <c r="K65" s="8"/>
+      <c r="L65" s="8"/>
+      <c r="M65" s="8"/>
+      <c r="R65" s="9"/>
+      <c r="T65" s="9"/>
+      <c r="U65" s="9"/>
+      <c r="V65" s="9"/>
+      <c r="W65" s="9"/>
+      <c r="X65" s="9"/>
+      <c r="Y65" s="9"/>
+      <c r="Z65" s="9"/>
+      <c r="AA65" s="9"/>
+    </row>
+    <row r="66" customHeight="1" spans="1:27">
+      <c r="A66" s="7"/>
+      <c r="K66" s="8"/>
+      <c r="L66" s="8"/>
+      <c r="M66" s="8"/>
+      <c r="R66" s="9"/>
+      <c r="T66" s="9"/>
+      <c r="U66" s="9"/>
+      <c r="V66" s="9"/>
+      <c r="W66" s="9"/>
+      <c r="X66" s="9"/>
+      <c r="Y66" s="9"/>
+      <c r="Z66" s="9"/>
+      <c r="AA66" s="9"/>
+    </row>
+    <row r="67" customHeight="1" spans="1:27">
+      <c r="A67" s="7"/>
+      <c r="K67" s="8"/>
+      <c r="L67" s="8"/>
+      <c r="M67" s="8"/>
+      <c r="R67" s="9"/>
+      <c r="T67" s="9"/>
+      <c r="U67" s="9"/>
+      <c r="V67" s="9"/>
+      <c r="W67" s="9"/>
+      <c r="X67" s="9"/>
+      <c r="Y67" s="9"/>
+      <c r="Z67" s="9"/>
+      <c r="AA67" s="9"/>
+    </row>
+    <row r="68" customHeight="1" spans="1:27">
+      <c r="A68" s="7"/>
+      <c r="K68" s="8"/>
+      <c r="L68" s="8"/>
+      <c r="M68" s="8"/>
+      <c r="R68" s="9"/>
+      <c r="T68" s="9"/>
+      <c r="U68" s="9"/>
+      <c r="V68" s="9"/>
+      <c r="W68" s="9"/>
+      <c r="X68" s="9"/>
+      <c r="Y68" s="9"/>
+      <c r="Z68" s="9"/>
+      <c r="AA68" s="9"/>
+    </row>
+    <row r="69" customHeight="1" spans="1:27">
+      <c r="A69" s="7"/>
+      <c r="K69" s="8"/>
+      <c r="L69" s="8"/>
+      <c r="M69" s="8"/>
+      <c r="R69" s="9"/>
+      <c r="T69" s="9"/>
+      <c r="U69" s="9"/>
+      <c r="V69" s="9"/>
+      <c r="W69" s="9"/>
+      <c r="X69" s="9"/>
+      <c r="Y69" s="9"/>
+      <c r="Z69" s="9"/>
+      <c r="AA69" s="9"/>
+    </row>
+    <row r="70" customHeight="1" spans="1:27">
+      <c r="A70" s="7"/>
+      <c r="K70" s="8"/>
+      <c r="L70" s="8"/>
+      <c r="M70" s="8"/>
+      <c r="R70" s="9"/>
+      <c r="T70" s="9"/>
+      <c r="U70" s="9"/>
+      <c r="V70" s="9"/>
+      <c r="W70" s="9"/>
+      <c r="X70" s="9"/>
+      <c r="Y70" s="9"/>
+      <c r="Z70" s="9"/>
+      <c r="AA70" s="9"/>
+    </row>
+    <row r="71" customHeight="1" spans="1:27">
+      <c r="A71" s="7"/>
+      <c r="K71" s="8"/>
+      <c r="L71" s="8"/>
+      <c r="M71" s="8"/>
+      <c r="R71" s="9"/>
+      <c r="T71" s="9"/>
+      <c r="U71" s="9"/>
+      <c r="V71" s="9"/>
+      <c r="W71" s="9"/>
+      <c r="X71" s="9"/>
+      <c r="Y71" s="9"/>
+      <c r="Z71" s="9"/>
+      <c r="AA71" s="9"/>
+    </row>
+    <row r="72" customHeight="1" spans="1:27">
+      <c r="A72" s="7"/>
+      <c r="K72" s="8"/>
+      <c r="L72" s="8"/>
+      <c r="M72" s="8"/>
+      <c r="R72" s="9"/>
+      <c r="T72" s="9"/>
+      <c r="U72" s="9"/>
+      <c r="V72" s="9"/>
+      <c r="W72" s="9"/>
+      <c r="X72" s="9"/>
+      <c r="Y72" s="9"/>
+      <c r="Z72" s="9"/>
+      <c r="AA72" s="9"/>
+    </row>
+    <row r="73" customHeight="1" spans="1:27">
+      <c r="A73" s="7"/>
+      <c r="K73" s="8"/>
+      <c r="L73" s="8"/>
+      <c r="M73" s="8"/>
+      <c r="R73" s="9"/>
+      <c r="T73" s="9"/>
+      <c r="U73" s="9"/>
+      <c r="V73" s="9"/>
+      <c r="W73" s="9"/>
+      <c r="X73" s="9"/>
+      <c r="Y73" s="9"/>
+      <c r="Z73" s="9"/>
+      <c r="AA73" s="9"/>
+    </row>
+    <row r="74" customHeight="1" spans="1:27">
+      <c r="A74" s="7"/>
+      <c r="K74" s="8"/>
+      <c r="L74" s="8"/>
+      <c r="M74" s="8"/>
+      <c r="R74" s="9"/>
+      <c r="T74" s="9"/>
+      <c r="U74" s="9"/>
+      <c r="V74" s="9"/>
+      <c r="W74" s="9"/>
+      <c r="X74" s="9"/>
+      <c r="Y74" s="9"/>
+      <c r="Z74" s="9"/>
+      <c r="AA74" s="9"/>
+    </row>
+    <row r="75" customHeight="1" spans="1:27">
+      <c r="A75" s="7"/>
+      <c r="K75" s="8"/>
+      <c r="L75" s="8"/>
+      <c r="M75" s="8"/>
+      <c r="R75" s="9"/>
+      <c r="T75" s="9"/>
+      <c r="U75" s="9"/>
+      <c r="V75" s="9"/>
+      <c r="W75" s="9"/>
+      <c r="X75" s="9"/>
+      <c r="Y75" s="9"/>
+      <c r="Z75" s="9"/>
+      <c r="AA75" s="9"/>
+    </row>
+    <row r="76" customHeight="1" spans="1:27">
+      <c r="A76" s="7"/>
+      <c r="K76" s="8"/>
+      <c r="L76" s="8"/>
+      <c r="M76" s="8"/>
+      <c r="R76" s="9"/>
+      <c r="T76" s="9"/>
+      <c r="U76" s="9"/>
+      <c r="V76" s="9"/>
+      <c r="W76" s="9"/>
+      <c r="X76" s="9"/>
+      <c r="Y76" s="9"/>
+      <c r="Z76" s="9"/>
+      <c r="AA76" s="9"/>
+    </row>
+    <row r="77" customHeight="1" spans="1:27">
+      <c r="A77" s="7"/>
+      <c r="K77" s="8"/>
+      <c r="L77" s="8"/>
+      <c r="M77" s="8"/>
+      <c r="R77" s="9"/>
+      <c r="T77" s="9"/>
+      <c r="U77" s="9"/>
+      <c r="V77" s="9"/>
+      <c r="W77" s="9"/>
+      <c r="X77" s="9"/>
+      <c r="Y77" s="9"/>
+      <c r="Z77" s="9"/>
+      <c r="AA77" s="9"/>
+    </row>
+    <row r="78" customHeight="1" spans="1:27">
+      <c r="A78" s="7"/>
+      <c r="K78" s="8"/>
+      <c r="L78" s="8"/>
+      <c r="M78" s="8"/>
+      <c r="R78" s="9"/>
+      <c r="T78" s="9"/>
+      <c r="U78" s="9"/>
+      <c r="V78" s="9"/>
+      <c r="W78" s="9"/>
+      <c r="X78" s="9"/>
+      <c r="Y78" s="9"/>
+      <c r="Z78" s="9"/>
+      <c r="AA78" s="9"/>
+    </row>
+    <row r="79" customHeight="1" spans="1:27">
+      <c r="A79" s="7"/>
+      <c r="K79" s="8"/>
+      <c r="L79" s="8"/>
+      <c r="M79" s="8"/>
+      <c r="R79" s="9"/>
+      <c r="T79" s="9"/>
+      <c r="U79" s="9"/>
+      <c r="V79" s="9"/>
+      <c r="W79" s="9"/>
+      <c r="X79" s="9"/>
+      <c r="Y79" s="9"/>
+      <c r="Z79" s="9"/>
+      <c r="AA79" s="9"/>
+    </row>
+    <row r="80" customHeight="1" spans="1:27">
+      <c r="A80" s="7"/>
+      <c r="K80" s="8"/>
+      <c r="L80" s="8"/>
+      <c r="M80" s="8"/>
+      <c r="R80" s="9"/>
+      <c r="T80" s="9"/>
+      <c r="U80" s="9"/>
+      <c r="V80" s="9"/>
+      <c r="W80" s="9"/>
+      <c r="X80" s="9"/>
+      <c r="Y80" s="9"/>
+      <c r="Z80" s="9"/>
+      <c r="AA80" s="9"/>
+    </row>
+    <row r="81" customHeight="1" spans="1:27">
+      <c r="A81" s="7"/>
+      <c r="K81" s="8"/>
+      <c r="L81" s="8"/>
+      <c r="M81" s="8"/>
+      <c r="R81" s="9"/>
+      <c r="T81" s="9"/>
+      <c r="U81" s="9"/>
+      <c r="V81" s="9"/>
+      <c r="W81" s="9"/>
+      <c r="X81" s="9"/>
+      <c r="Y81" s="9"/>
+      <c r="Z81" s="9"/>
+      <c r="AA81" s="9"/>
+    </row>
+    <row r="82" customHeight="1" spans="1:27">
+      <c r="A82" s="7"/>
+      <c r="K82" s="8"/>
+      <c r="L82" s="8"/>
+      <c r="M82" s="8"/>
+      <c r="R82" s="9"/>
+      <c r="T82" s="9"/>
+      <c r="U82" s="9"/>
+      <c r="V82" s="9"/>
+      <c r="W82" s="9"/>
+      <c r="X82" s="9"/>
+      <c r="Y82" s="9"/>
+      <c r="Z82" s="9"/>
+      <c r="AA82" s="9"/>
+    </row>
+    <row r="83" customHeight="1" spans="1:27">
+      <c r="A83" s="7"/>
+      <c r="K83" s="8"/>
+      <c r="L83" s="8"/>
+      <c r="M83" s="8"/>
+      <c r="R83" s="9"/>
+      <c r="T83" s="9"/>
+      <c r="U83" s="9"/>
+      <c r="V83" s="9"/>
+      <c r="W83" s="9"/>
+      <c r="X83" s="9"/>
+      <c r="Y83" s="9"/>
+      <c r="Z83" s="9"/>
+      <c r="AA83" s="9"/>
+    </row>
+    <row r="84" customHeight="1" spans="1:27">
+      <c r="A84" s="7"/>
+      <c r="K84" s="8"/>
+      <c r="L84" s="8"/>
+      <c r="M84" s="8"/>
+      <c r="R84" s="9"/>
+      <c r="T84" s="9"/>
+      <c r="U84" s="9"/>
+      <c r="V84" s="9"/>
+      <c r="W84" s="9"/>
+      <c r="X84" s="9"/>
+      <c r="Y84" s="9"/>
+      <c r="Z84" s="9"/>
+      <c r="AA84" s="9"/>
+    </row>
+    <row r="85" customHeight="1" spans="1:27">
+      <c r="A85" s="7"/>
+      <c r="K85" s="8"/>
+      <c r="L85" s="8"/>
+      <c r="M85" s="8"/>
+      <c r="R85" s="9"/>
+      <c r="T85" s="9"/>
+      <c r="U85" s="9"/>
+      <c r="V85" s="9"/>
+      <c r="W85" s="9"/>
+      <c r="X85" s="9"/>
+      <c r="Y85" s="9"/>
+      <c r="Z85" s="9"/>
+      <c r="AA85" s="9"/>
+    </row>
+    <row r="86" customHeight="1" spans="1:27">
+      <c r="A86" s="7"/>
+      <c r="K86" s="8"/>
+      <c r="L86" s="8"/>
+      <c r="M86" s="8"/>
+      <c r="R86" s="9"/>
+      <c r="T86" s="9"/>
+      <c r="U86" s="9"/>
+      <c r="V86" s="9"/>
+      <c r="W86" s="9"/>
+      <c r="X86" s="9"/>
+      <c r="Y86" s="9"/>
+      <c r="Z86" s="9"/>
+      <c r="AA86" s="9"/>
+    </row>
+    <row r="87" customHeight="1" spans="1:27">
+      <c r="A87" s="7"/>
+      <c r="K87" s="8"/>
+      <c r="L87" s="8"/>
+      <c r="M87" s="8"/>
+      <c r="R87" s="9"/>
+      <c r="T87" s="9"/>
+      <c r="U87" s="9"/>
+      <c r="V87" s="9"/>
+      <c r="W87" s="9"/>
+      <c r="X87" s="9"/>
+      <c r="Y87" s="9"/>
+      <c r="Z87" s="9"/>
+      <c r="AA87" s="9"/>
+    </row>
+    <row r="88" customHeight="1" spans="1:27">
+      <c r="A88" s="7"/>
+      <c r="K88" s="8"/>
+      <c r="L88" s="8"/>
+      <c r="M88" s="8"/>
+      <c r="R88" s="9"/>
+      <c r="T88" s="9"/>
+      <c r="U88" s="9"/>
+      <c r="V88" s="9"/>
+      <c r="W88" s="9"/>
+      <c r="X88" s="9"/>
+      <c r="Y88" s="9"/>
+      <c r="Z88" s="9"/>
+      <c r="AA88" s="9"/>
+    </row>
+    <row r="89" customHeight="1" spans="1:27">
+      <c r="A89" s="7"/>
+      <c r="K89" s="8"/>
+      <c r="L89" s="8"/>
+      <c r="M89" s="8"/>
+      <c r="R89" s="9"/>
+      <c r="T89" s="9"/>
+      <c r="U89" s="9"/>
+      <c r="V89" s="9"/>
+      <c r="W89" s="9"/>
+      <c r="X89" s="9"/>
+      <c r="Y89" s="9"/>
+      <c r="Z89" s="9"/>
+      <c r="AA89" s="9"/>
+    </row>
+    <row r="90" customHeight="1" spans="1:27">
+      <c r="A90" s="7"/>
+      <c r="K90" s="8"/>
+      <c r="L90" s="8"/>
+      <c r="M90" s="8"/>
+      <c r="R90" s="9"/>
+      <c r="T90" s="9"/>
+      <c r="U90" s="9"/>
+      <c r="V90" s="9"/>
+      <c r="W90" s="9"/>
+      <c r="X90" s="9"/>
+      <c r="Y90" s="9"/>
+      <c r="Z90" s="9"/>
+      <c r="AA90" s="9"/>
+    </row>
+    <row r="91" customHeight="1" spans="1:27">
+      <c r="A91" s="7"/>
+      <c r="K91" s="8"/>
+      <c r="L91" s="8"/>
+      <c r="M91" s="8"/>
+      <c r="R91" s="9"/>
+      <c r="T91" s="9"/>
+      <c r="U91" s="9"/>
+      <c r="V91" s="9"/>
+      <c r="W91" s="9"/>
+      <c r="X91" s="9"/>
+      <c r="Y91" s="9"/>
+      <c r="Z91" s="9"/>
+      <c r="AA91" s="9"/>
+    </row>
+    <row r="92" customHeight="1" spans="1:27">
+      <c r="A92" s="7"/>
+      <c r="K92" s="8"/>
+      <c r="L92" s="8"/>
+      <c r="M92" s="8"/>
+      <c r="R92" s="9"/>
+      <c r="T92" s="9"/>
+      <c r="U92" s="9"/>
+      <c r="V92" s="9"/>
+      <c r="W92" s="9"/>
+      <c r="X92" s="9"/>
+      <c r="Y92" s="9"/>
+      <c r="Z92" s="9"/>
+      <c r="AA92" s="9"/>
+    </row>
+    <row r="93" customHeight="1" spans="1:27">
+      <c r="A93" s="7"/>
+      <c r="K93" s="8"/>
+      <c r="L93" s="8"/>
+      <c r="M93" s="8"/>
+      <c r="R93" s="9"/>
+      <c r="T93" s="9"/>
+      <c r="U93" s="9"/>
+      <c r="V93" s="9"/>
+      <c r="W93" s="9"/>
+      <c r="X93" s="9"/>
+      <c r="Y93" s="9"/>
+      <c r="Z93" s="9"/>
+      <c r="AA93" s="9"/>
+    </row>
+    <row r="94" customHeight="1" spans="1:27">
+      <c r="A94" s="7"/>
+      <c r="K94" s="8"/>
+      <c r="L94" s="8"/>
+      <c r="M94" s="8"/>
+      <c r="R94" s="9"/>
+      <c r="T94" s="9"/>
+      <c r="U94" s="9"/>
+      <c r="V94" s="9"/>
+      <c r="W94" s="9"/>
+      <c r="X94" s="9"/>
+      <c r="Y94" s="9"/>
+      <c r="Z94" s="9"/>
+      <c r="AA94" s="9"/>
+    </row>
+    <row r="95" customHeight="1" spans="1:27">
+      <c r="A95" s="7"/>
+      <c r="K95" s="8"/>
+      <c r="L95" s="8"/>
+      <c r="M95" s="8"/>
+      <c r="R95" s="9"/>
+      <c r="T95" s="9"/>
+      <c r="U95" s="9"/>
+      <c r="V95" s="9"/>
+      <c r="W95" s="9"/>
+      <c r="X95" s="9"/>
+      <c r="Y95" s="9"/>
+      <c r="Z95" s="9"/>
+      <c r="AA95" s="9"/>
+    </row>
+    <row r="96" customHeight="1" spans="1:27">
+      <c r="A96" s="7"/>
+      <c r="K96" s="8"/>
+      <c r="L96" s="8"/>
+      <c r="M96" s="8"/>
+      <c r="R96" s="9"/>
+      <c r="T96" s="9"/>
+      <c r="U96" s="9"/>
+      <c r="V96" s="9"/>
+      <c r="W96" s="9"/>
+      <c r="X96" s="9"/>
+      <c r="Y96" s="9"/>
+      <c r="Z96" s="9"/>
+      <c r="AA96" s="9"/>
+    </row>
+    <row r="97" customHeight="1" spans="1:27">
+      <c r="A97" s="7"/>
+      <c r="K97" s="8"/>
+      <c r="L97" s="8"/>
+      <c r="M97" s="8"/>
+      <c r="R97" s="9"/>
+      <c r="T97" s="9"/>
+      <c r="U97" s="9"/>
+      <c r="V97" s="9"/>
+      <c r="W97" s="9"/>
+      <c r="X97" s="9"/>
+      <c r="Y97" s="9"/>
+      <c r="Z97" s="9"/>
+      <c r="AA97" s="9"/>
+    </row>
+    <row r="98" customHeight="1" spans="1:27">
+      <c r="A98" s="7"/>
+      <c r="K98" s="8"/>
+      <c r="L98" s="8"/>
+      <c r="M98" s="8"/>
+      <c r="R98" s="9"/>
+      <c r="T98" s="9"/>
+      <c r="U98" s="9"/>
+      <c r="V98" s="9"/>
+      <c r="W98" s="9"/>
+      <c r="X98" s="9"/>
+      <c r="Y98" s="9"/>
+      <c r="Z98" s="9"/>
+      <c r="AA98" s="9"/>
+    </row>
+    <row r="99" customHeight="1" spans="1:27">
+      <c r="A99" s="7"/>
+      <c r="K99" s="8"/>
+      <c r="L99" s="8"/>
+      <c r="M99" s="8"/>
+      <c r="R99" s="9"/>
+      <c r="T99" s="9"/>
+      <c r="U99" s="9"/>
+      <c r="V99" s="9"/>
+      <c r="W99" s="9"/>
+      <c r="X99" s="9"/>
+      <c r="Y99" s="9"/>
+      <c r="Z99" s="9"/>
+      <c r="AA99" s="9"/>
+    </row>
+    <row r="100" customHeight="1" spans="1:27">
+      <c r="A100" s="7"/>
+      <c r="K100" s="8"/>
+      <c r="L100" s="8"/>
+      <c r="M100" s="8"/>
+      <c r="R100" s="9"/>
+      <c r="T100" s="9"/>
+      <c r="U100" s="9"/>
+      <c r="V100" s="9"/>
+      <c r="W100" s="9"/>
+      <c r="X100" s="9"/>
+      <c r="Y100" s="9"/>
+      <c r="Z100" s="9"/>
+      <c r="AA100" s="9"/>
+    </row>
+    <row r="101" customHeight="1" spans="1:27">
+      <c r="A101" s="7"/>
+      <c r="K101" s="8"/>
+      <c r="L101" s="8"/>
+      <c r="M101" s="8"/>
+      <c r="R101" s="9"/>
+      <c r="T101" s="9"/>
+      <c r="U101" s="9"/>
+      <c r="V101" s="9"/>
+      <c r="W101" s="9"/>
+      <c r="X101" s="9"/>
+      <c r="Y101" s="9"/>
+      <c r="Z101" s="9"/>
+      <c r="AA101" s="9"/>
+    </row>
+    <row r="102" customHeight="1" spans="1:27">
+      <c r="A102" s="7"/>
+      <c r="K102" s="8"/>
+      <c r="L102" s="8"/>
+      <c r="M102" s="8"/>
+      <c r="R102" s="9"/>
+      <c r="T102" s="9"/>
+      <c r="U102" s="9"/>
+      <c r="V102" s="9"/>
+      <c r="W102" s="9"/>
+      <c r="X102" s="9"/>
+      <c r="Y102" s="9"/>
+      <c r="Z102" s="9"/>
+      <c r="AA102" s="9"/>
+    </row>
+    <row r="103" customHeight="1" spans="1:27">
+      <c r="A103" s="7"/>
+      <c r="K103" s="8"/>
+      <c r="L103" s="8"/>
+      <c r="M103" s="8"/>
+      <c r="R103" s="9"/>
+      <c r="T103" s="9"/>
+      <c r="U103" s="9"/>
+      <c r="V103" s="9"/>
+      <c r="W103" s="9"/>
+      <c r="X103" s="9"/>
+      <c r="Y103" s="9"/>
+      <c r="Z103" s="9"/>
+      <c r="AA103" s="9"/>
+    </row>
+    <row r="104" customHeight="1" spans="1:27">
+      <c r="A104" s="7"/>
+      <c r="K104" s="8"/>
+      <c r="L104" s="8"/>
+      <c r="M104" s="8"/>
+      <c r="R104" s="9"/>
+      <c r="T104" s="9"/>
+      <c r="U104" s="9"/>
+      <c r="V104" s="9"/>
+      <c r="W104" s="9"/>
+      <c r="X104" s="9"/>
+      <c r="Y104" s="9"/>
+      <c r="Z104" s="9"/>
+      <c r="AA104" s="9"/>
+    </row>
+    <row r="105" customHeight="1" spans="1:27">
+      <c r="A105" s="7"/>
+      <c r="K105" s="8"/>
+      <c r="L105" s="8"/>
+      <c r="M105" s="8"/>
+      <c r="R105" s="9"/>
+      <c r="T105" s="9"/>
+      <c r="U105" s="9"/>
+      <c r="V105" s="9"/>
+      <c r="W105" s="9"/>
+      <c r="X105" s="9"/>
+      <c r="Y105" s="9"/>
+      <c r="Z105" s="9"/>
+      <c r="AA105" s="9"/>
+    </row>
+    <row r="106" customHeight="1" spans="1:27">
+      <c r="A106" s="7"/>
+      <c r="K106" s="8"/>
+      <c r="L106" s="8"/>
+      <c r="M106" s="8"/>
+      <c r="R106" s="9"/>
+      <c r="T106" s="9"/>
+      <c r="U106" s="9"/>
+      <c r="V106" s="9"/>
+      <c r="W106" s="9"/>
+      <c r="X106" s="9"/>
+      <c r="Y106" s="9"/>
+      <c r="Z106" s="9"/>
+      <c r="AA106" s="9"/>
+    </row>
+    <row r="107" customHeight="1" spans="1:27">
+      <c r="A107" s="7"/>
+      <c r="K107" s="8"/>
+      <c r="L107" s="8"/>
+      <c r="M107" s="8"/>
+      <c r="R107" s="9"/>
+      <c r="T107" s="9"/>
+      <c r="U107" s="9"/>
+      <c r="V107" s="9"/>
+      <c r="W107" s="9"/>
+      <c r="X107" s="9"/>
+      <c r="Y107" s="9"/>
+      <c r="Z107" s="9"/>
+      <c r="AA107" s="9"/>
+    </row>
+    <row r="108" customHeight="1" spans="1:27">
+      <c r="A108" s="7"/>
+      <c r="K108" s="8"/>
+      <c r="L108" s="8"/>
+      <c r="M108" s="8"/>
+      <c r="R108" s="9"/>
+      <c r="T108" s="9"/>
+      <c r="U108" s="9"/>
+      <c r="V108" s="9"/>
+      <c r="W108" s="9"/>
+      <c r="X108" s="9"/>
+      <c r="Y108" s="9"/>
+      <c r="Z108" s="9"/>
+      <c r="AA108" s="9"/>
+    </row>
+    <row r="109" customHeight="1" spans="1:27">
+      <c r="A109" s="7"/>
+      <c r="K109" s="8"/>
+      <c r="L109" s="8"/>
+      <c r="M109" s="8"/>
+      <c r="R109" s="9"/>
+      <c r="T109" s="9"/>
+      <c r="U109" s="9"/>
+      <c r="V109" s="9"/>
+      <c r="W109" s="9"/>
+      <c r="X109" s="9"/>
+      <c r="Y109" s="9"/>
+      <c r="Z109" s="9"/>
+      <c r="AA109" s="9"/>
+    </row>
+    <row r="110" customHeight="1" spans="1:27">
+      <c r="A110" s="7"/>
+      <c r="K110" s="8"/>
+      <c r="L110" s="8"/>
+      <c r="M110" s="8"/>
+      <c r="R110" s="9"/>
+      <c r="T110" s="9"/>
+      <c r="U110" s="9"/>
+      <c r="V110" s="9"/>
+      <c r="W110" s="9"/>
+      <c r="X110" s="9"/>
+      <c r="Y110" s="9"/>
+      <c r="Z110" s="9"/>
+      <c r="AA110" s="9"/>
+    </row>
+    <row r="111" customHeight="1" spans="1:27">
+      <c r="A111" s="7"/>
+      <c r="K111" s="8"/>
+      <c r="L111" s="8"/>
+      <c r="M111" s="8"/>
+      <c r="R111" s="9"/>
+      <c r="T111" s="9"/>
+      <c r="U111" s="9"/>
+      <c r="V111" s="9"/>
+      <c r="W111" s="9"/>
+      <c r="X111" s="9"/>
+      <c r="Y111" s="9"/>
+      <c r="Z111" s="9"/>
+      <c r="AA111" s="9"/>
+    </row>
+    <row r="112" customHeight="1" spans="1:27">
+      <c r="A112" s="7"/>
+      <c r="K112" s="8"/>
+      <c r="L112" s="8"/>
+      <c r="M112" s="8"/>
+      <c r="R112" s="9"/>
+      <c r="T112" s="9"/>
+      <c r="U112" s="9"/>
+      <c r="V112" s="9"/>
+      <c r="W112" s="9"/>
+      <c r="X112" s="9"/>
+      <c r="Y112" s="9"/>
+      <c r="Z112" s="9"/>
+      <c r="AA112" s="9"/>
+    </row>
+    <row r="113" customHeight="1" spans="1:27">
+      <c r="A113" s="7"/>
+      <c r="K113" s="8"/>
+      <c r="L113" s="8"/>
+      <c r="M113" s="8"/>
+      <c r="R113" s="9"/>
+      <c r="T113" s="9"/>
+      <c r="U113" s="9"/>
+      <c r="V113" s="9"/>
+      <c r="W113" s="9"/>
+      <c r="X113" s="9"/>
+      <c r="Y113" s="9"/>
+      <c r="Z113" s="9"/>
+      <c r="AA113" s="9"/>
+    </row>
+    <row r="114" customHeight="1" spans="1:27">
+      <c r="A114" s="7"/>
+      <c r="K114" s="8"/>
+      <c r="L114" s="8"/>
+      <c r="M114" s="8"/>
+      <c r="R114" s="9"/>
+      <c r="T114" s="9"/>
+      <c r="U114" s="9"/>
+      <c r="V114" s="9"/>
+      <c r="W114" s="9"/>
+      <c r="X114" s="9"/>
+      <c r="Y114" s="9"/>
+      <c r="Z114" s="9"/>
+      <c r="AA114" s="9"/>
+    </row>
+    <row r="115" customHeight="1" spans="1:27">
+      <c r="A115" s="7"/>
+      <c r="K115" s="8"/>
+      <c r="L115" s="8"/>
+      <c r="M115" s="8"/>
+      <c r="R115" s="9"/>
+      <c r="T115" s="9"/>
+      <c r="U115" s="9"/>
+      <c r="V115" s="9"/>
+      <c r="W115" s="9"/>
+      <c r="X115" s="9"/>
+      <c r="Y115" s="9"/>
+      <c r="Z115" s="9"/>
+      <c r="AA115" s="9"/>
+    </row>
+    <row r="116" customHeight="1" spans="1:27">
+      <c r="A116" s="7"/>
+      <c r="K116" s="8"/>
+      <c r="L116" s="8"/>
+      <c r="M116" s="8"/>
+      <c r="R116" s="9"/>
+      <c r="T116" s="9"/>
+      <c r="U116" s="9"/>
+      <c r="V116" s="9"/>
+      <c r="W116" s="9"/>
+      <c r="X116" s="9"/>
+      <c r="Y116" s="9"/>
+      <c r="Z116" s="9"/>
+      <c r="AA116" s="9"/>
+    </row>
+    <row r="117" customHeight="1" spans="1:27">
+      <c r="A117" s="7"/>
+      <c r="K117" s="8"/>
+      <c r="L117" s="8"/>
+      <c r="M117" s="8"/>
+      <c r="R117" s="9"/>
+      <c r="T117" s="9"/>
+      <c r="U117" s="9"/>
+      <c r="V117" s="9"/>
+      <c r="W117" s="9"/>
+      <c r="X117" s="9"/>
+      <c r="Y117" s="9"/>
+      <c r="Z117" s="9"/>
+      <c r="AA117" s="9"/>
+    </row>
+    <row r="118" customHeight="1" spans="1:27">
+      <c r="A118" s="7"/>
+      <c r="K118" s="8"/>
+      <c r="L118" s="8"/>
+      <c r="M118" s="8"/>
+      <c r="R118" s="9"/>
+      <c r="T118" s="9"/>
+      <c r="U118" s="9"/>
+      <c r="V118" s="9"/>
+      <c r="W118" s="9"/>
+      <c r="X118" s="9"/>
+      <c r="Y118" s="9"/>
+      <c r="Z118" s="9"/>
+      <c r="AA118" s="9"/>
+    </row>
+    <row r="119" customHeight="1" spans="1:27">
+      <c r="A119" s="7"/>
+      <c r="K119" s="8"/>
+      <c r="L119" s="8"/>
+      <c r="M119" s="8"/>
+      <c r="R119" s="9"/>
+      <c r="T119" s="9"/>
+      <c r="U119" s="9"/>
+      <c r="V119" s="9"/>
+      <c r="W119" s="9"/>
+      <c r="X119" s="9"/>
+      <c r="Y119" s="9"/>
+      <c r="Z119" s="9"/>
+      <c r="AA119" s="9"/>
+    </row>
+    <row r="120" customHeight="1" spans="1:27">
+      <c r="A120" s="7"/>
+      <c r="K120" s="8"/>
+      <c r="L120" s="8"/>
+      <c r="M120" s="8"/>
+      <c r="R120" s="9"/>
+      <c r="T120" s="9"/>
+      <c r="U120" s="9"/>
+      <c r="V120" s="9"/>
+      <c r="W120" s="9"/>
+      <c r="X120" s="9"/>
+      <c r="Y120" s="9"/>
+      <c r="Z120" s="9"/>
+      <c r="AA120" s="9"/>
+    </row>
+    <row r="121" customHeight="1" spans="1:27">
+      <c r="A121" s="7"/>
+      <c r="K121" s="8"/>
+      <c r="L121" s="8"/>
+      <c r="M121" s="8"/>
+      <c r="R121" s="9"/>
+      <c r="T121" s="9"/>
+      <c r="U121" s="9"/>
+      <c r="V121" s="9"/>
+      <c r="W121" s="9"/>
+      <c r="X121" s="9"/>
+      <c r="Y121" s="9"/>
+      <c r="Z121" s="9"/>
+      <c r="AA121" s="9"/>
+    </row>
+    <row r="122" customHeight="1" spans="1:27">
+      <c r="A122" s="7"/>
+      <c r="K122" s="8"/>
+      <c r="L122" s="8"/>
+      <c r="M122" s="8"/>
+      <c r="R122" s="9"/>
+      <c r="T122" s="9"/>
+      <c r="U122" s="9"/>
+      <c r="V122" s="9"/>
+      <c r="W122" s="9"/>
+      <c r="X122" s="9"/>
+      <c r="Y122" s="9"/>
+      <c r="Z122" s="9"/>
+      <c r="AA122" s="9"/>
+    </row>
+    <row r="123" customHeight="1" spans="1:27">
+      <c r="A123" s="7"/>
+      <c r="K123" s="8"/>
+      <c r="L123" s="8"/>
+      <c r="M123" s="8"/>
+      <c r="R123" s="9"/>
+      <c r="T123" s="9"/>
+      <c r="U123" s="9"/>
+      <c r="V123" s="9"/>
+      <c r="W123" s="9"/>
+      <c r="X123" s="9"/>
+      <c r="Y123" s="9"/>
+      <c r="Z123" s="9"/>
+      <c r="AA123" s="9"/>
+    </row>
+    <row r="124" customHeight="1" spans="1:27">
+      <c r="A124" s="7"/>
+      <c r="K124" s="8"/>
+      <c r="L124" s="8"/>
+      <c r="M124" s="8"/>
+      <c r="R124" s="9"/>
+      <c r="T124" s="9"/>
+      <c r="U124" s="9"/>
+      <c r="V124" s="9"/>
+      <c r="W124" s="9"/>
+      <c r="X124" s="9"/>
+      <c r="Y124" s="9"/>
+      <c r="Z124" s="9"/>
+      <c r="AA124" s="9"/>
+    </row>
+    <row r="125" customHeight="1" spans="1:27">
+      <c r="A125" s="7"/>
+      <c r="K125" s="8"/>
+      <c r="L125" s="8"/>
+      <c r="M125" s="8"/>
+      <c r="R125" s="9"/>
+      <c r="T125" s="9"/>
+      <c r="U125" s="9"/>
+      <c r="V125" s="9"/>
+      <c r="W125" s="9"/>
+      <c r="X125" s="9"/>
+      <c r="Y125" s="9"/>
+      <c r="Z125" s="9"/>
+      <c r="AA125" s="9"/>
+    </row>
+    <row r="126" customHeight="1" spans="1:27">
+      <c r="A126" s="7"/>
+      <c r="K126" s="8"/>
+      <c r="L126" s="8"/>
+      <c r="M126" s="8"/>
+      <c r="R126" s="9"/>
+      <c r="T126" s="9"/>
+      <c r="U126" s="9"/>
+      <c r="V126" s="9"/>
+      <c r="W126" s="9"/>
+      <c r="X126" s="9"/>
+      <c r="Y126" s="9"/>
+      <c r="Z126" s="9"/>
+      <c r="AA126" s="9"/>
+    </row>
+    <row r="127" customHeight="1" spans="1:27">
+      <c r="A127" s="7"/>
+      <c r="K127" s="8"/>
+      <c r="L127" s="8"/>
+      <c r="M127" s="8"/>
+      <c r="R127" s="9"/>
+      <c r="T127" s="9"/>
+      <c r="U127" s="9"/>
+      <c r="V127" s="9"/>
+      <c r="W127" s="9"/>
+      <c r="X127" s="9"/>
+      <c r="Y127" s="9"/>
+      <c r="Z127" s="9"/>
+      <c r="AA127" s="9"/>
+    </row>
+    <row r="128" customHeight="1" spans="1:27">
+      <c r="A128" s="7"/>
+      <c r="K128" s="8"/>
+      <c r="L128" s="8"/>
+      <c r="M128" s="8"/>
+      <c r="R128" s="9"/>
+      <c r="T128" s="9"/>
+      <c r="U128" s="9"/>
+      <c r="V128" s="9"/>
+      <c r="W128" s="9"/>
+      <c r="X128" s="9"/>
+      <c r="Y128" s="9"/>
+      <c r="Z128" s="9"/>
+      <c r="AA128" s="9"/>
+    </row>
+    <row r="129" customHeight="1" spans="1:27">
+      <c r="A129" s="7"/>
+      <c r="K129" s="8"/>
+      <c r="L129" s="8"/>
+      <c r="M129" s="8"/>
+      <c r="R129" s="9"/>
+      <c r="T129" s="9"/>
+      <c r="U129" s="9"/>
+      <c r="V129" s="9"/>
+      <c r="W129" s="9"/>
+      <c r="X129" s="9"/>
+      <c r="Y129" s="9"/>
+      <c r="Z129" s="9"/>
+      <c r="AA129" s="9"/>
+    </row>
+    <row r="130" customHeight="1" spans="1:27">
+      <c r="A130" s="7"/>
+      <c r="K130" s="8"/>
+      <c r="L130" s="8"/>
+      <c r="M130" s="8"/>
+      <c r="R130" s="9"/>
+      <c r="T130" s="9"/>
+      <c r="U130" s="9"/>
+      <c r="V130" s="9"/>
+      <c r="W130" s="9"/>
+      <c r="X130" s="9"/>
+      <c r="Y130" s="9"/>
+      <c r="Z130" s="9"/>
+      <c r="AA130" s="9"/>
+    </row>
+    <row r="131" customHeight="1" spans="1:27">
+      <c r="A131" s="7"/>
+      <c r="K131" s="8"/>
+      <c r="L131" s="8"/>
+      <c r="M131" s="8"/>
+      <c r="R131" s="9"/>
+      <c r="T131" s="9"/>
+      <c r="U131" s="9"/>
+      <c r="V131" s="9"/>
+      <c r="W131" s="9"/>
+      <c r="X131" s="9"/>
+      <c r="Y131" s="9"/>
+      <c r="Z131" s="9"/>
+      <c r="AA131" s="9"/>
+    </row>
+    <row r="132" customHeight="1" spans="1:27">
+      <c r="A132" s="7"/>
+      <c r="K132" s="8"/>
+      <c r="L132" s="8"/>
+      <c r="M132" s="8"/>
+      <c r="R132" s="9"/>
+      <c r="T132" s="9"/>
+      <c r="U132" s="9"/>
+      <c r="V132" s="9"/>
+      <c r="W132" s="9"/>
+      <c r="X132" s="9"/>
+      <c r="Y132" s="9"/>
+      <c r="Z132" s="9"/>
+      <c r="AA132" s="9"/>
+    </row>
+    <row r="133" customHeight="1" spans="1:27">
+      <c r="A133" s="7"/>
+      <c r="K133" s="8"/>
+      <c r="L133" s="8"/>
+      <c r="M133" s="8"/>
+      <c r="R133" s="9"/>
+      <c r="T133" s="9"/>
+      <c r="U133" s="9"/>
+      <c r="V133" s="9"/>
+      <c r="W133" s="9"/>
+      <c r="X133" s="9"/>
+      <c r="Y133" s="9"/>
+      <c r="Z133" s="9"/>
+      <c r="AA133" s="9"/>
+    </row>
+    <row r="134" customHeight="1" spans="1:27">
+      <c r="A134" s="7"/>
+      <c r="K134" s="8"/>
+      <c r="L134" s="8"/>
+      <c r="M134" s="8"/>
+      <c r="R134" s="9"/>
+      <c r="T134" s="9"/>
+      <c r="U134" s="9"/>
+      <c r="V134" s="9"/>
+      <c r="W134" s="9"/>
+      <c r="X134" s="9"/>
+      <c r="Y134" s="9"/>
+      <c r="Z134" s="9"/>
+      <c r="AA134" s="9"/>
+    </row>
+    <row r="135" customHeight="1" spans="1:27">
+      <c r="A135" s="7"/>
+      <c r="K135" s="8"/>
+      <c r="L135" s="8"/>
+      <c r="M135" s="8"/>
+      <c r="R135" s="9"/>
+      <c r="T135" s="9"/>
+      <c r="U135" s="9"/>
+      <c r="V135" s="9"/>
+      <c r="W135" s="9"/>
+      <c r="X135" s="9"/>
+      <c r="Y135" s="9"/>
+      <c r="Z135" s="9"/>
+      <c r="AA135" s="9"/>
+    </row>
+    <row r="136" customHeight="1" spans="1:27">
+      <c r="A136" s="7"/>
+      <c r="K136" s="8"/>
+      <c r="L136" s="8"/>
+      <c r="M136" s="8"/>
+      <c r="R136" s="9"/>
+      <c r="T136" s="9"/>
+      <c r="U136" s="9"/>
+      <c r="V136" s="9"/>
+      <c r="W136" s="9"/>
+      <c r="X136" s="9"/>
+      <c r="Y136" s="9"/>
+      <c r="Z136" s="9"/>
+      <c r="AA136" s="9"/>
+    </row>
+    <row r="137" customHeight="1" spans="1:27">
+      <c r="A137" s="7"/>
+      <c r="K137" s="8"/>
+      <c r="L137" s="8"/>
+      <c r="M137" s="8"/>
+      <c r="R137" s="9"/>
+      <c r="T137" s="9"/>
+      <c r="U137" s="9"/>
+      <c r="V137" s="9"/>
+      <c r="W137" s="9"/>
+      <c r="X137" s="9"/>
+      <c r="Y137" s="9"/>
+      <c r="Z137" s="9"/>
+      <c r="AA137" s="9"/>
+    </row>
+    <row r="138" customHeight="1" spans="1:27">
+      <c r="A138" s="7"/>
+      <c r="K138" s="8"/>
+      <c r="L138" s="8"/>
+      <c r="M138" s="8"/>
+      <c r="R138" s="9"/>
+      <c r="T138" s="9"/>
+      <c r="U138" s="9"/>
+      <c r="V138" s="9"/>
+      <c r="W138" s="9"/>
+      <c r="X138" s="9"/>
+      <c r="Y138" s="9"/>
+      <c r="Z138" s="9"/>
+      <c r="AA138" s="9"/>
+    </row>
+    <row r="139" customHeight="1" spans="1:27">
+      <c r="A139" s="7"/>
+      <c r="K139" s="8"/>
+      <c r="L139" s="8"/>
+      <c r="M139" s="8"/>
+      <c r="R139" s="9"/>
+      <c r="T139" s="9"/>
+      <c r="U139" s="9"/>
+      <c r="V139" s="9"/>
+      <c r="W139" s="9"/>
+      <c r="X139" s="9"/>
+      <c r="Y139" s="9"/>
+      <c r="Z139" s="9"/>
+      <c r="AA139" s="9"/>
+    </row>
+    <row r="140" customHeight="1" spans="1:27">
+      <c r="A140" s="7"/>
+      <c r="K140" s="8"/>
+      <c r="L140" s="8"/>
+      <c r="M140" s="8"/>
+      <c r="R140" s="9"/>
+      <c r="T140" s="9"/>
+      <c r="U140" s="9"/>
+      <c r="V140" s="9"/>
+      <c r="W140" s="9"/>
+      <c r="X140" s="9"/>
+      <c r="Y140" s="9"/>
+      <c r="Z140" s="9"/>
+      <c r="AA140" s="9"/>
+    </row>
+    <row r="141" customHeight="1" spans="1:27">
+      <c r="A141" s="7"/>
+      <c r="K141" s="8"/>
+      <c r="L141" s="8"/>
+      <c r="M141" s="8"/>
+      <c r="R141" s="9"/>
+      <c r="T141" s="9"/>
+      <c r="U141" s="9"/>
+      <c r="V141" s="9"/>
+      <c r="W141" s="9"/>
+      <c r="X141" s="9"/>
+      <c r="Y141" s="9"/>
+      <c r="Z141" s="9"/>
+      <c r="AA141" s="9"/>
+    </row>
+    <row r="142" customHeight="1" spans="1:27">
+      <c r="A142" s="7"/>
+      <c r="K142" s="8"/>
+      <c r="L142" s="8"/>
+      <c r="M142" s="8"/>
+      <c r="R142" s="9"/>
+      <c r="T142" s="9"/>
+      <c r="U142" s="9"/>
+      <c r="V142" s="9"/>
+      <c r="W142" s="9"/>
+      <c r="X142" s="9"/>
+      <c r="Y142" s="9"/>
+      <c r="Z142" s="9"/>
+      <c r="AA142" s="9"/>
+    </row>
+    <row r="143" customHeight="1" spans="1:27">
+      <c r="A143" s="7"/>
+      <c r="K143" s="8"/>
+      <c r="L143" s="8"/>
+      <c r="M143" s="8"/>
+      <c r="R143" s="9"/>
+      <c r="T143" s="9"/>
+      <c r="U143" s="9"/>
+      <c r="V143" s="9"/>
+      <c r="W143" s="9"/>
+      <c r="X143" s="9"/>
+      <c r="Y143" s="9"/>
+      <c r="Z143" s="9"/>
+      <c r="AA143" s="9"/>
+    </row>
+    <row r="144" customHeight="1" spans="1:27">
+      <c r="A144" s="7"/>
+      <c r="K144" s="8"/>
+      <c r="L144" s="8"/>
+      <c r="M144" s="8"/>
+      <c r="R144" s="9"/>
+      <c r="T144" s="9"/>
+      <c r="U144" s="9"/>
+      <c r="V144" s="9"/>
+      <c r="W144" s="9"/>
+      <c r="X144" s="9"/>
+      <c r="Y144" s="9"/>
+      <c r="Z144" s="9"/>
+      <c r="AA144" s="9"/>
+    </row>
+    <row r="145" customHeight="1" spans="1:27">
+      <c r="A145" s="7"/>
+      <c r="K145" s="8"/>
+      <c r="L145" s="8"/>
+      <c r="M145" s="8"/>
+      <c r="R145" s="9"/>
+      <c r="T145" s="9"/>
+      <c r="U145" s="9"/>
+      <c r="V145" s="9"/>
+      <c r="W145" s="9"/>
+      <c r="X145" s="9"/>
+      <c r="Y145" s="9"/>
+      <c r="Z145" s="9"/>
+      <c r="AA145" s="9"/>
+    </row>
+    <row r="146" customHeight="1" spans="1:27">
+      <c r="A146" s="7"/>
+      <c r="K146" s="8"/>
+      <c r="L146" s="8"/>
+      <c r="M146" s="8"/>
+      <c r="R146" s="9"/>
+      <c r="T146" s="9"/>
+      <c r="U146" s="9"/>
+      <c r="V146" s="9"/>
+      <c r="W146" s="9"/>
+      <c r="X146" s="9"/>
+      <c r="Y146" s="9"/>
+      <c r="Z146" s="9"/>
+      <c r="AA146" s="9"/>
+    </row>
+    <row r="147" customHeight="1" spans="1:27">
+      <c r="A147" s="7"/>
+      <c r="K147" s="8"/>
+      <c r="L147" s="8"/>
+      <c r="M147" s="8"/>
+      <c r="R147" s="9"/>
+      <c r="T147" s="9"/>
+      <c r="U147" s="9"/>
+      <c r="V147" s="9"/>
+      <c r="W147" s="9"/>
+      <c r="X147" s="9"/>
+      <c r="Y147" s="9"/>
+      <c r="Z147" s="9"/>
+      <c r="AA147" s="9"/>
+    </row>
+    <row r="148" customHeight="1" spans="1:27">
+      <c r="A148" s="7"/>
+      <c r="K148" s="8"/>
+      <c r="L148" s="8"/>
+      <c r="M148" s="8"/>
+      <c r="R148" s="9"/>
+      <c r="T148" s="9"/>
+      <c r="U148" s="9"/>
+      <c r="V148" s="9"/>
+      <c r="W148" s="9"/>
+      <c r="X148" s="9"/>
+      <c r="Y148" s="9"/>
+      <c r="Z148" s="9"/>
+      <c r="AA148" s="9"/>
+    </row>
+    <row r="149" customHeight="1" spans="1:27">
+      <c r="A149" s="7"/>
+      <c r="K149" s="8"/>
+      <c r="L149" s="8"/>
+      <c r="M149" s="8"/>
+      <c r="R149" s="9"/>
+      <c r="T149" s="9"/>
+      <c r="U149" s="9"/>
+      <c r="V149" s="9"/>
+      <c r="W149" s="9"/>
+      <c r="X149" s="9"/>
+      <c r="Y149" s="9"/>
+      <c r="Z149" s="9"/>
+      <c r="AA149" s="9"/>
+    </row>
+    <row r="150" customHeight="1" spans="1:27">
+      <c r="A150" s="7"/>
+      <c r="K150" s="8"/>
+      <c r="L150" s="8"/>
+      <c r="M150" s="8"/>
+      <c r="R150" s="9"/>
+      <c r="T150" s="9"/>
+      <c r="U150" s="9"/>
+      <c r="V150" s="9"/>
+      <c r="W150" s="9"/>
+      <c r="X150" s="9"/>
+      <c r="Y150" s="9"/>
+      <c r="Z150" s="9"/>
+      <c r="AA150" s="9"/>
+    </row>
+    <row r="151" customHeight="1" spans="1:27">
+      <c r="A151" s="7"/>
+      <c r="K151" s="8"/>
+      <c r="L151" s="8"/>
+      <c r="M151" s="8"/>
+      <c r="R151" s="9"/>
+      <c r="T151" s="9"/>
+      <c r="U151" s="9"/>
+      <c r="V151" s="9"/>
+      <c r="W151" s="9"/>
+      <c r="X151" s="9"/>
+      <c r="Y151" s="9"/>
+      <c r="Z151" s="9"/>
+      <c r="AA151" s="9"/>
+    </row>
+    <row r="152" customHeight="1" spans="1:27">
+      <c r="A152" s="7"/>
+      <c r="K152" s="8"/>
+      <c r="L152" s="8"/>
+      <c r="M152" s="8"/>
+      <c r="R152" s="9"/>
+      <c r="T152" s="9"/>
+      <c r="U152" s="9"/>
+      <c r="V152" s="9"/>
+      <c r="W152" s="9"/>
+      <c r="X152" s="9"/>
+      <c r="Y152" s="9"/>
+      <c r="Z152" s="9"/>
+      <c r="AA152" s="9"/>
+    </row>
+    <row r="153" customHeight="1" spans="1:27">
+      <c r="A153" s="7"/>
+      <c r="K153" s="8"/>
+      <c r="L153" s="8"/>
+      <c r="M153" s="8"/>
+      <c r="R153" s="9"/>
+      <c r="T153" s="9"/>
+      <c r="U153" s="9"/>
+      <c r="V153" s="9"/>
+      <c r="W153" s="9"/>
+      <c r="X153" s="9"/>
+      <c r="Y153" s="9"/>
+      <c r="Z153" s="9"/>
+      <c r="AA153" s="9"/>
+    </row>
+    <row r="154" customHeight="1" spans="1:27">
+      <c r="A154" s="7"/>
+      <c r="K154" s="8"/>
+      <c r="L154" s="8"/>
+      <c r="M154" s="8"/>
+      <c r="R154" s="9"/>
+      <c r="T154" s="9"/>
+      <c r="U154" s="9"/>
+      <c r="V154" s="9"/>
+      <c r="W154" s="9"/>
+      <c r="X154" s="9"/>
+      <c r="Y154" s="9"/>
+      <c r="Z154" s="9"/>
+      <c r="AA154" s="9"/>
+    </row>
+    <row r="155" customHeight="1" spans="1:27">
+      <c r="A155" s="7"/>
+      <c r="K155" s="8"/>
+      <c r="L155" s="8"/>
+      <c r="M155" s="8"/>
+      <c r="R155" s="9"/>
+      <c r="T155" s="9"/>
+      <c r="U155" s="9"/>
+      <c r="V155" s="9"/>
+      <c r="W155" s="9"/>
+      <c r="X155" s="9"/>
+      <c r="Y155" s="9"/>
+      <c r="Z155" s="9"/>
+      <c r="AA155" s="9"/>
+    </row>
+    <row r="156" customHeight="1" spans="1:27">
+      <c r="A156" s="7"/>
+      <c r="K156" s="8"/>
+      <c r="L156" s="8"/>
+      <c r="M156" s="8"/>
+      <c r="R156" s="9"/>
+      <c r="T156" s="9"/>
+      <c r="U156" s="9"/>
+      <c r="V156" s="9"/>
+      <c r="W156" s="9"/>
+      <c r="X156" s="9"/>
+      <c r="Y156" s="9"/>
+      <c r="Z156" s="9"/>
+      <c r="AA156" s="9"/>
+    </row>
+    <row r="157" customHeight="1" spans="1:27">
+      <c r="A157" s="7"/>
+      <c r="K157" s="8"/>
+      <c r="L157" s="8"/>
+      <c r="M157" s="8"/>
+      <c r="R157" s="9"/>
+      <c r="T157" s="9"/>
+      <c r="U157" s="9"/>
+      <c r="V157" s="9"/>
+      <c r="W157" s="9"/>
+      <c r="X157" s="9"/>
+      <c r="Y157" s="9"/>
+      <c r="Z157" s="9"/>
+      <c r="AA157" s="9"/>
+    </row>
+    <row r="158" customHeight="1" spans="1:27">
+      <c r="A158" s="7"/>
+      <c r="K158" s="8"/>
+      <c r="L158" s="8"/>
+      <c r="M158" s="8"/>
+      <c r="R158" s="9"/>
+      <c r="T158" s="9"/>
+      <c r="U158" s="9"/>
+      <c r="V158" s="9"/>
+      <c r="W158" s="9"/>
+      <c r="X158" s="9"/>
+      <c r="Y158" s="9"/>
+      <c r="Z158" s="9"/>
+      <c r="AA158" s="9"/>
+    </row>
+    <row r="159" customHeight="1" spans="1:27">
+      <c r="A159" s="7"/>
+      <c r="K159" s="8"/>
+      <c r="L159" s="8"/>
+      <c r="M159" s="8"/>
+      <c r="R159" s="9"/>
+      <c r="T159" s="9"/>
+      <c r="U159" s="9"/>
+      <c r="V159" s="9"/>
+      <c r="W159" s="9"/>
+      <c r="X159" s="9"/>
+      <c r="Y159" s="9"/>
+      <c r="Z159" s="9"/>
+      <c r="AA159" s="9"/>
+    </row>
+    <row r="160" customHeight="1" spans="1:27">
+      <c r="A160" s="7"/>
+      <c r="K160" s="8"/>
+      <c r="L160" s="8"/>
+      <c r="M160" s="8"/>
+      <c r="R160" s="9"/>
+      <c r="T160" s="9"/>
+      <c r="U160" s="9"/>
+      <c r="V160" s="9"/>
+      <c r="W160" s="9"/>
+      <c r="X160" s="9"/>
+      <c r="Y160" s="9"/>
+      <c r="Z160" s="9"/>
+      <c r="AA160" s="9"/>
+    </row>
+    <row r="161" customHeight="1" spans="1:27">
+      <c r="A161" s="7"/>
+      <c r="K161" s="8"/>
+      <c r="L161" s="8"/>
+      <c r="M161" s="8"/>
+      <c r="R161" s="9"/>
+      <c r="T161" s="9"/>
+      <c r="U161" s="9"/>
+      <c r="V161" s="9"/>
+      <c r="W161" s="9"/>
+      <c r="X161" s="9"/>
+      <c r="Y161" s="9"/>
+      <c r="Z161" s="9"/>
+      <c r="AA161" s="9"/>
+    </row>
+    <row r="162" customHeight="1" spans="1:27">
+      <c r="A162" s="7"/>
+      <c r="K162" s="8"/>
+      <c r="L162" s="8"/>
+      <c r="M162" s="8"/>
+      <c r="R162" s="9"/>
+      <c r="T162" s="9"/>
+      <c r="U162" s="9"/>
+      <c r="V162" s="9"/>
+      <c r="W162" s="9"/>
+      <c r="X162" s="9"/>
+      <c r="Y162" s="9"/>
+      <c r="Z162" s="9"/>
+      <c r="AA162" s="9"/>
+    </row>
+    <row r="163" customHeight="1" spans="1:27">
+      <c r="A163" s="7"/>
+      <c r="K163" s="8"/>
+      <c r="L163" s="8"/>
+      <c r="M163" s="8"/>
+      <c r="R163" s="9"/>
+      <c r="T163" s="9"/>
+      <c r="U163" s="9"/>
+      <c r="V163" s="9"/>
+      <c r="W163" s="9"/>
+      <c r="X163" s="9"/>
+      <c r="Y163" s="9"/>
+      <c r="Z163" s="9"/>
+      <c r="AA163" s="9"/>
+    </row>
+    <row r="164" customHeight="1" spans="1:27">
+      <c r="A164" s="7"/>
+      <c r="K164" s="8"/>
+      <c r="L164" s="8"/>
+      <c r="M164" s="8"/>
+      <c r="R164" s="9"/>
+      <c r="T164" s="9"/>
+      <c r="U164" s="9"/>
+      <c r="V164" s="9"/>
+      <c r="W164" s="9"/>
+      <c r="X164" s="9"/>
+      <c r="Y164" s="9"/>
+      <c r="Z164" s="9"/>
+      <c r="AA164" s="9"/>
+    </row>
+    <row r="165" customHeight="1" spans="1:27">
+      <c r="A165" s="7"/>
+      <c r="K165" s="8"/>
+      <c r="L165" s="8"/>
+      <c r="M165" s="8"/>
+      <c r="R165" s="9"/>
+      <c r="T165" s="9"/>
+      <c r="U165" s="9"/>
+      <c r="V165" s="9"/>
+      <c r="W165" s="9"/>
+      <c r="X165" s="9"/>
+      <c r="Y165" s="9"/>
+      <c r="Z165" s="9"/>
+      <c r="AA165" s="9"/>
+    </row>
+    <row r="166" customHeight="1" spans="1:27">
+      <c r="A166" s="7"/>
+      <c r="K166" s="8"/>
+      <c r="L166" s="8"/>
+      <c r="M166" s="8"/>
+      <c r="R166" s="9"/>
+      <c r="T166" s="9"/>
+      <c r="U166" s="9"/>
+      <c r="V166" s="9"/>
+      <c r="W166" s="9"/>
+      <c r="X166" s="9"/>
+      <c r="Y166" s="9"/>
+      <c r="Z166" s="9"/>
+      <c r="AA166" s="9"/>
+    </row>
+    <row r="167" customHeight="1" spans="1:27">
+      <c r="A167" s="7"/>
+      <c r="K167" s="8"/>
+      <c r="L167" s="8"/>
+      <c r="M167" s="8"/>
+      <c r="R167" s="9"/>
+      <c r="T167" s="9"/>
+      <c r="U167" s="9"/>
+      <c r="V167" s="9"/>
+      <c r="W167" s="9"/>
+      <c r="X167" s="9"/>
+      <c r="Y167" s="9"/>
+      <c r="Z167" s="9"/>
+      <c r="AA167" s="9"/>
+    </row>
+    <row r="168" customHeight="1" spans="1:27">
+      <c r="A168" s="7"/>
+      <c r="K168" s="8"/>
+      <c r="L168" s="8"/>
+      <c r="M168" s="8"/>
+      <c r="R168" s="9"/>
+      <c r="T168" s="9"/>
+      <c r="U168" s="9"/>
+      <c r="V168" s="9"/>
+      <c r="W168" s="9"/>
+      <c r="X168" s="9"/>
+      <c r="Y168" s="9"/>
+      <c r="Z168" s="9"/>
+      <c r="AA168" s="9"/>
+    </row>
+    <row r="169" customHeight="1" spans="1:27">
+      <c r="A169" s="7"/>
+      <c r="K169" s="8"/>
+      <c r="L169" s="8"/>
+      <c r="M169" s="8"/>
+      <c r="R169" s="9"/>
+      <c r="T169" s="9"/>
+      <c r="U169" s="9"/>
+      <c r="V169" s="9"/>
+      <c r="W169" s="9"/>
+      <c r="X169" s="9"/>
+      <c r="Y169" s="9"/>
+      <c r="Z169" s="9"/>
+      <c r="AA169" s="9"/>
+    </row>
+    <row r="170" customHeight="1" spans="1:27">
+      <c r="A170" s="7"/>
+      <c r="K170" s="8"/>
+      <c r="L170" s="8"/>
+      <c r="M170" s="8"/>
+      <c r="R170" s="9"/>
+      <c r="T170" s="9"/>
+      <c r="U170" s="9"/>
+      <c r="V170" s="9"/>
+      <c r="W170" s="9"/>
+      <c r="X170" s="9"/>
+      <c r="Y170" s="9"/>
+      <c r="Z170" s="9"/>
+      <c r="AA170" s="9"/>
+    </row>
+    <row r="171" customHeight="1" spans="1:27">
+      <c r="A171" s="7"/>
+      <c r="K171" s="8"/>
+      <c r="L171" s="8"/>
+      <c r="M171" s="8"/>
+      <c r="R171" s="9"/>
+      <c r="T171" s="9"/>
+      <c r="U171" s="9"/>
+      <c r="V171" s="9"/>
+      <c r="W171" s="9"/>
+      <c r="X171" s="9"/>
+      <c r="Y171" s="9"/>
+      <c r="Z171" s="9"/>
+      <c r="AA171" s="9"/>
+    </row>
+    <row r="172" customHeight="1" spans="1:27">
+      <c r="A172" s="7"/>
+      <c r="K172" s="8"/>
+      <c r="L172" s="8"/>
+      <c r="M172" s="8"/>
+      <c r="R172" s="9"/>
+      <c r="T172" s="9"/>
+      <c r="U172" s="9"/>
+      <c r="V172" s="9"/>
+      <c r="W172" s="9"/>
+      <c r="X172" s="9"/>
+      <c r="Y172" s="9"/>
+      <c r="Z172" s="9"/>
+      <c r="AA172" s="9"/>
+    </row>
+    <row r="173" customHeight="1" spans="1:27">
+      <c r="A173" s="7"/>
+      <c r="K173" s="8"/>
+      <c r="L173" s="8"/>
+      <c r="M173" s="8"/>
+      <c r="R173" s="9"/>
+      <c r="T173" s="9"/>
+      <c r="U173" s="9"/>
+      <c r="V173" s="9"/>
+      <c r="W173" s="9"/>
+      <c r="X173" s="9"/>
+      <c r="Y173" s="9"/>
+      <c r="Z173" s="9"/>
+      <c r="AA173" s="9"/>
+    </row>
+    <row r="174" customHeight="1" spans="1:27">
+      <c r="A174" s="7"/>
+      <c r="K174" s="8"/>
+      <c r="L174" s="8"/>
+      <c r="M174" s="8"/>
+      <c r="R174" s="9"/>
+      <c r="T174" s="9"/>
+      <c r="U174" s="9"/>
+      <c r="V174" s="9"/>
+      <c r="W174" s="9"/>
+      <c r="X174" s="9"/>
+      <c r="Y174" s="9"/>
+      <c r="Z174" s="9"/>
+      <c r="AA174" s="9"/>
+    </row>
+    <row r="175" customHeight="1" spans="1:27">
+      <c r="A175" s="7"/>
+      <c r="K175" s="8"/>
+      <c r="L175" s="8"/>
+      <c r="M175" s="8"/>
+      <c r="R175" s="9"/>
+      <c r="T175" s="9"/>
+      <c r="U175" s="9"/>
+      <c r="V175" s="9"/>
+      <c r="W175" s="9"/>
+      <c r="X175" s="9"/>
+      <c r="Y175" s="9"/>
+      <c r="Z175" s="9"/>
+      <c r="AA175" s="9"/>
+    </row>
+    <row r="176" customHeight="1" spans="1:27">
+      <c r="A176" s="7"/>
+      <c r="K176" s="8"/>
+      <c r="L176" s="8"/>
+      <c r="M176" s="8"/>
+      <c r="R176" s="9"/>
+      <c r="T176" s="9"/>
+      <c r="U176" s="9"/>
+      <c r="V176" s="9"/>
+      <c r="W176" s="9"/>
+      <c r="X176" s="9"/>
+      <c r="Y176" s="9"/>
+      <c r="Z176" s="9"/>
+      <c r="AA176" s="9"/>
+    </row>
+    <row r="177" customHeight="1" spans="1:27">
+      <c r="A177" s="7"/>
+      <c r="K177" s="8"/>
+      <c r="L177" s="8"/>
+      <c r="M177" s="8"/>
+      <c r="R177" s="9"/>
+      <c r="T177" s="9"/>
+      <c r="U177" s="9"/>
+      <c r="V177" s="9"/>
+      <c r="W177" s="9"/>
+      <c r="X177" s="9"/>
+      <c r="Y177" s="9"/>
+      <c r="Z177" s="9"/>
+      <c r="AA177" s="9"/>
+    </row>
+    <row r="178" customHeight="1" spans="1:27">
+      <c r="A178" s="7"/>
+      <c r="K178" s="8"/>
+      <c r="L178" s="8"/>
+      <c r="M178" s="8"/>
+      <c r="R178" s="9"/>
+      <c r="T178" s="9"/>
+      <c r="U178" s="9"/>
+      <c r="V178" s="9"/>
+      <c r="W178" s="9"/>
+      <c r="X178" s="9"/>
+      <c r="Y178" s="9"/>
+      <c r="Z178" s="9"/>
+      <c r="AA178" s="9"/>
+    </row>
+    <row r="179" customHeight="1" spans="1:27">
+      <c r="A179" s="7"/>
+      <c r="K179" s="8"/>
+      <c r="L179" s="8"/>
+      <c r="M179" s="8"/>
+      <c r="R179" s="9"/>
+      <c r="T179" s="9"/>
+      <c r="U179" s="9"/>
+      <c r="V179" s="9"/>
+      <c r="W179" s="9"/>
+      <c r="X179" s="9"/>
+      <c r="Y179" s="9"/>
+      <c r="Z179" s="9"/>
+      <c r="AA179" s="9"/>
+    </row>
+    <row r="180" customHeight="1" spans="1:27">
+      <c r="A180" s="7"/>
+      <c r="K180" s="8"/>
+      <c r="L180" s="8"/>
+      <c r="M180" s="8"/>
+      <c r="R180" s="9"/>
+      <c r="T180" s="9"/>
+      <c r="U180" s="9"/>
+      <c r="V180" s="9"/>
+      <c r="W180" s="9"/>
+      <c r="X180" s="9"/>
+      <c r="Y180" s="9"/>
+      <c r="Z180" s="9"/>
+      <c r="AA180" s="9"/>
+    </row>
+    <row r="181" customHeight="1" spans="1:27">
+      <c r="A181" s="7"/>
+      <c r="K181" s="8"/>
+      <c r="L181" s="8"/>
+      <c r="M181" s="8"/>
+      <c r="R181" s="9"/>
+      <c r="T181" s="9"/>
+      <c r="U181" s="9"/>
+      <c r="V181" s="9"/>
+      <c r="W181" s="9"/>
+      <c r="X181" s="9"/>
+      <c r="Y181" s="9"/>
+      <c r="Z181" s="9"/>
+      <c r="AA181" s="9"/>
+    </row>
+    <row r="182" customHeight="1" spans="1:27">
+      <c r="A182" s="7"/>
+      <c r="K182" s="8"/>
+      <c r="L182" s="8"/>
+      <c r="M182" s="8"/>
+      <c r="R182" s="9"/>
+      <c r="T182" s="9"/>
+      <c r="U182" s="9"/>
+      <c r="V182" s="9"/>
+      <c r="W182" s="9"/>
+      <c r="X182" s="9"/>
+      <c r="Y182" s="9"/>
+      <c r="Z182" s="9"/>
+      <c r="AA182" s="9"/>
+    </row>
+    <row r="183" customHeight="1" spans="1:27">
+      <c r="A183" s="7"/>
+      <c r="K183" s="8"/>
+      <c r="L183" s="8"/>
+      <c r="M183" s="8"/>
+      <c r="R183" s="9"/>
+      <c r="T183" s="9"/>
+      <c r="U183" s="9"/>
+      <c r="V183" s="9"/>
+      <c r="W183" s="9"/>
+      <c r="X183" s="9"/>
+      <c r="Y183" s="9"/>
+      <c r="Z183" s="9"/>
+      <c r="AA183" s="9"/>
+    </row>
+    <row r="184" customHeight="1" spans="1:27">
+      <c r="A184" s="7"/>
+      <c r="K184" s="8"/>
+      <c r="L184" s="8"/>
+      <c r="M184" s="8"/>
+      <c r="R184" s="9"/>
+      <c r="T184" s="9"/>
+      <c r="U184" s="9"/>
+      <c r="V184" s="9"/>
+      <c r="W184" s="9"/>
+      <c r="X184" s="9"/>
+      <c r="Y184" s="9"/>
+      <c r="Z184" s="9"/>
+      <c r="AA184" s="9"/>
+    </row>
+    <row r="185" customHeight="1" spans="1:27">
+      <c r="A185" s="7"/>
+      <c r="K185" s="8"/>
+      <c r="L185" s="8"/>
+      <c r="M185" s="8"/>
+      <c r="R185" s="9"/>
+      <c r="T185" s="9"/>
+      <c r="U185" s="9"/>
+      <c r="V185" s="9"/>
+      <c r="W185" s="9"/>
+      <c r="X185" s="9"/>
+      <c r="Y185" s="9"/>
+      <c r="Z185" s="9"/>
+      <c r="AA185" s="9"/>
+    </row>
+    <row r="186" customHeight="1" spans="1:27">
+      <c r="A186" s="7"/>
+      <c r="K186" s="8"/>
+      <c r="L186" s="8"/>
+      <c r="M186" s="8"/>
+      <c r="R186" s="9"/>
+      <c r="T186" s="9"/>
+      <c r="U186" s="9"/>
+      <c r="V186" s="9"/>
+      <c r="W186" s="9"/>
+      <c r="X186" s="9"/>
+      <c r="Y186" s="9"/>
+      <c r="Z186" s="9"/>
+      <c r="AA186" s="9"/>
+    </row>
+    <row r="187" customHeight="1" spans="1:27">
+      <c r="A187" s="7"/>
+      <c r="K187" s="8"/>
+      <c r="L187" s="8"/>
+      <c r="M187" s="8"/>
+      <c r="R187" s="9"/>
+      <c r="T187" s="9"/>
+      <c r="U187" s="9"/>
+      <c r="V187" s="9"/>
+      <c r="W187" s="9"/>
+      <c r="X187" s="9"/>
+      <c r="Y187" s="9"/>
+      <c r="Z187" s="9"/>
+      <c r="AA187" s="9"/>
+    </row>
+    <row r="188" customHeight="1" spans="1:27">
+      <c r="A188" s="7"/>
+      <c r="K188" s="8"/>
+      <c r="L188" s="8"/>
+      <c r="M188" s="8"/>
+      <c r="R188" s="9"/>
+      <c r="T188" s="9"/>
+      <c r="U188" s="9"/>
+      <c r="V188" s="9"/>
+      <c r="W188" s="9"/>
+      <c r="X188" s="9"/>
+      <c r="Y188" s="9"/>
+      <c r="Z188" s="9"/>
+      <c r="AA188" s="9"/>
+    </row>
+    <row r="189" customHeight="1" spans="1:27">
+      <c r="A189" s="7"/>
+      <c r="K189" s="8"/>
+      <c r="L189" s="8"/>
+      <c r="M189" s="8"/>
+      <c r="R189" s="9"/>
+      <c r="T189" s="9"/>
+      <c r="U189" s="9"/>
+      <c r="V189" s="9"/>
+      <c r="W189" s="9"/>
+      <c r="X189" s="9"/>
+      <c r="Y189" s="9"/>
+      <c r="Z189" s="9"/>
+      <c r="AA189" s="9"/>
+    </row>
+    <row r="190" customHeight="1" spans="1:27">
+      <c r="A190" s="7"/>
+      <c r="K190" s="8"/>
+      <c r="L190" s="8"/>
+      <c r="M190" s="8"/>
+      <c r="R190" s="9"/>
+      <c r="T190" s="9"/>
+      <c r="U190" s="9"/>
+      <c r="V190" s="9"/>
+      <c r="W190" s="9"/>
+      <c r="X190" s="9"/>
+      <c r="Y190" s="9"/>
+      <c r="Z190" s="9"/>
+      <c r="AA190" s="9"/>
+    </row>
+    <row r="191" customHeight="1" spans="1:27">
+      <c r="A191" s="7"/>
+      <c r="K191" s="8"/>
+      <c r="L191" s="8"/>
+      <c r="M191" s="8"/>
+      <c r="R191" s="9"/>
+      <c r="T191" s="9"/>
+      <c r="U191" s="9"/>
+      <c r="V191" s="9"/>
+      <c r="W191" s="9"/>
+      <c r="X191" s="9"/>
+      <c r="Y191" s="9"/>
+      <c r="Z191" s="9"/>
+      <c r="AA191" s="9"/>
+    </row>
+    <row r="192" customHeight="1" spans="1:27">
+      <c r="A192" s="7"/>
+      <c r="K192" s="8"/>
+      <c r="L192" s="8"/>
+      <c r="M192" s="8"/>
+      <c r="R192" s="9"/>
+      <c r="T192" s="9"/>
+      <c r="U192" s="9"/>
+      <c r="V192" s="9"/>
+      <c r="W192" s="9"/>
+      <c r="X192" s="9"/>
+      <c r="Y192" s="9"/>
+      <c r="Z192" s="9"/>
+      <c r="AA192" s="9"/>
+    </row>
+    <row r="193" customHeight="1" spans="1:27">
+      <c r="A193" s="7"/>
+      <c r="K193" s="8"/>
+      <c r="L193" s="8"/>
+      <c r="M193" s="8"/>
+      <c r="R193" s="9"/>
+      <c r="T193" s="9"/>
+      <c r="U193" s="9"/>
+      <c r="V193" s="9"/>
+      <c r="W193" s="9"/>
+      <c r="X193" s="9"/>
+      <c r="Y193" s="9"/>
+      <c r="Z193" s="9"/>
+      <c r="AA193" s="9"/>
+    </row>
+    <row r="194" customHeight="1" spans="1:27">
+      <c r="A194" s="7"/>
+      <c r="K194" s="8"/>
+      <c r="L194" s="8"/>
+      <c r="M194" s="8"/>
+      <c r="R194" s="9"/>
+      <c r="T194" s="9"/>
+      <c r="U194" s="9"/>
+      <c r="V194" s="9"/>
+      <c r="W194" s="9"/>
+      <c r="X194" s="9"/>
+      <c r="Y194" s="9"/>
+      <c r="Z194" s="9"/>
+      <c r="AA194" s="9"/>
+    </row>
+    <row r="195" customHeight="1" spans="1:27">
+      <c r="A195" s="7"/>
+      <c r="K195" s="8"/>
+      <c r="L195" s="8"/>
+      <c r="M195" s="8"/>
+      <c r="R195" s="9"/>
+      <c r="T195" s="9"/>
+      <c r="U195" s="9"/>
+      <c r="V195" s="9"/>
+      <c r="W195" s="9"/>
+      <c r="X195" s="9"/>
+      <c r="Y195" s="9"/>
+      <c r="Z195" s="9"/>
+      <c r="AA195" s="9"/>
+    </row>
+    <row r="196" customHeight="1" spans="1:27">
+      <c r="A196" s="7"/>
+      <c r="K196" s="8"/>
+      <c r="L196" s="8"/>
+      <c r="M196" s="8"/>
+      <c r="R196" s="9"/>
+      <c r="T196" s="9"/>
+      <c r="U196" s="9"/>
+      <c r="V196" s="9"/>
+      <c r="W196" s="9"/>
+      <c r="X196" s="9"/>
+      <c r="Y196" s="9"/>
+      <c r="Z196" s="9"/>
+      <c r="AA196" s="9"/>
+    </row>
+    <row r="197" customHeight="1" spans="1:27">
+      <c r="A197" s="7"/>
+      <c r="K197" s="8"/>
+      <c r="L197" s="8"/>
+      <c r="M197" s="8"/>
+      <c r="R197" s="9"/>
+      <c r="T197" s="9"/>
+      <c r="U197" s="9"/>
+      <c r="V197" s="9"/>
+      <c r="W197" s="9"/>
+      <c r="X197" s="9"/>
+      <c r="Y197" s="9"/>
+      <c r="Z197" s="9"/>
+      <c r="AA197" s="9"/>
+    </row>
+    <row r="198" customHeight="1" spans="1:27">
+      <c r="A198" s="7"/>
+      <c r="K198" s="8"/>
+      <c r="L198" s="8"/>
+      <c r="M198" s="8"/>
+      <c r="R198" s="9"/>
+      <c r="T198" s="9"/>
+      <c r="U198" s="9"/>
+      <c r="V198" s="9"/>
+      <c r="W198" s="9"/>
+      <c r="X198" s="9"/>
+      <c r="Y198" s="9"/>
+      <c r="Z198" s="9"/>
+      <c r="AA198" s="9"/>
+    </row>
+    <row r="199" customHeight="1" spans="1:27">
+      <c r="A199" s="7"/>
+      <c r="K199" s="8"/>
+      <c r="L199" s="8"/>
+      <c r="M199" s="8"/>
+      <c r="R199" s="9"/>
+      <c r="T199" s="9"/>
+      <c r="U199" s="9"/>
+      <c r="V199" s="9"/>
+      <c r="W199" s="9"/>
+      <c r="X199" s="9"/>
+      <c r="Y199" s="9"/>
+      <c r="Z199" s="9"/>
+      <c r="AA199" s="9"/>
+    </row>
+    <row r="200" customHeight="1" spans="1:27">
+      <c r="A200" s="7"/>
+      <c r="K200" s="8"/>
+      <c r="L200" s="8"/>
+      <c r="M200" s="8"/>
+      <c r="R200" s="9"/>
+      <c r="T200" s="9"/>
+      <c r="U200" s="9"/>
+      <c r="V200" s="9"/>
+      <c r="W200" s="9"/>
+      <c r="X200" s="9"/>
+      <c r="Y200" s="9"/>
+      <c r="Z200" s="9"/>
+      <c r="AA200" s="9"/>
+    </row>
+  </sheetData>
+  <sheetProtection insertHyperlinks="0" autoFilter="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="X3:X83"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" customHeight="1"/>
+  <cols>
+    <col min="1" max="23" width="9" style="1"/>
+    <col min="24" max="24" width="49" style="2" customWidth="1"/>
+    <col min="25" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" ht="404" customHeight="1" spans="24:24">
+      <c r="X3" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="83" ht="46" customHeight="1" spans="24:24">
+      <c r="X83" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection insertHyperlinks="0" autoFilter="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/assets/demand_template.xlsx
+++ b/assets/demand_template.xlsx
@@ -19,11 +19,11 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="44">
   <si>
-    <t>机务二队定检需求单（XXXX.XX.XX）
+    <t>定检中队定检需求单（XXXX.XX.XX）
 （B-XXXX XXA）</t>
   </si>
   <si>
-    <t>一、定检运行条件要求（机务二队、MCC、维修支援中队负责）</t>
+    <t>一、定检运行条件要求（定检中队、MCC、维修支援中队负责）</t>
   </si>
   <si>
     <t>项目</t>
@@ -83,7 +83,7 @@
     <t>AOG带件情况</t>
   </si>
   <si>
-    <t>二、本次定检工装\航材需求（机务二队、MCC、维修支援中队负责）</t>
+    <t>二、本次定检工装\航材需求（定检中队、MCC、维修支援中队负责）</t>
   </si>
   <si>
     <t>定检专业
@@ -145,7 +145,7 @@
     <t>电子</t>
   </si>
   <si>
-    <t>三、备用航材需求(机务二队、MCC负责)</t>
+    <t>三、备用航材需求(定检中队、MCC负责)</t>
   </si>
   <si>
     <t>专业</t>
